--- a/Templates/bulkImport/config/construct_RSDL_config_sslr.xlsx
+++ b/Templates/bulkImport/config/construct_RSDL_config_sslr.xlsx
@@ -1,86 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9024"/>
-  </bookViews>
   <sheets>
-    <sheet name="construct_RSDL_config_sarawak" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="construct_RSDL_config_sarawak" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>USER</author>
-  </authors>
-  <commentList>
-    <comment ref="B5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AE5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -353,923 +280,65 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="3">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="9">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
+  <borders count="1">
+    <border/>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1459,53 +528,53 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AQ1000"/>
-  <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.287037037037" customWidth="1"/>
-    <col min="2" max="2" width="11.1388888888889" customWidth="1"/>
-    <col min="3" max="3" width="23.5740740740741" customWidth="1"/>
-    <col min="4" max="4" width="14.5740740740741" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.5740740740741" customWidth="1"/>
-    <col min="7" max="7" width="12.8611111111111" customWidth="1"/>
-    <col min="8" max="8" width="18.287037037037" customWidth="1"/>
-    <col min="9" max="9" width="23.4259259259259" customWidth="1"/>
-    <col min="10" max="10" width="21.712962962963" customWidth="1"/>
-    <col min="11" max="11" width="27.712962962963" customWidth="1"/>
-    <col min="12" max="12" width="32.4259259259259" customWidth="1"/>
-    <col min="13" max="13" width="30.287037037037" customWidth="1"/>
-    <col min="14" max="14" width="16.1388888888889" customWidth="1"/>
-    <col min="15" max="16" width="17.8611111111111" customWidth="1"/>
-    <col min="17" max="17" width="17.5740740740741" customWidth="1"/>
-    <col min="18" max="18" width="14.287037037037" customWidth="1"/>
-    <col min="19" max="19" width="22.8611111111111" customWidth="1"/>
-    <col min="20" max="20" width="16.1388888888889" customWidth="1"/>
-    <col min="21" max="21" width="21.8611111111111" customWidth="1"/>
-    <col min="22" max="22" width="18.1388888888889" customWidth="1"/>
-    <col min="23" max="23" width="20.4259259259259" customWidth="1"/>
-    <col min="24" max="24" width="8.86111111111111" customWidth="1"/>
-    <col min="25" max="25" width="17.287037037037" customWidth="1"/>
-    <col min="26" max="26" width="13.1388888888889" customWidth="1"/>
-    <col min="27" max="27" width="21.712962962963" customWidth="1"/>
-    <col min="28" max="28" width="23.287037037037" customWidth="1"/>
-    <col min="29" max="29" width="24.712962962963" customWidth="1"/>
-    <col min="30" max="30" width="21.1388888888889" customWidth="1"/>
-    <col min="31" max="32" width="21" customWidth="1"/>
-    <col min="33" max="33" width="21.5740740740741" customWidth="1"/>
-    <col min="34" max="34" width="24.5740740740741" customWidth="1"/>
-    <col min="35" max="35" width="21.8611111111111" customWidth="1"/>
-    <col min="36" max="43" width="24.8611111111111" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10.29"/>
+    <col customWidth="1" min="2" max="2" width="11.14"/>
+    <col customWidth="1" min="3" max="3" width="23.57"/>
+    <col customWidth="1" min="4" max="4" width="14.57"/>
+    <col customWidth="1" min="5" max="5" width="14.0"/>
+    <col customWidth="1" min="6" max="6" width="15.57"/>
+    <col customWidth="1" min="7" max="7" width="12.86"/>
+    <col customWidth="1" min="8" max="8" width="18.29"/>
+    <col customWidth="1" min="9" max="9" width="23.43"/>
+    <col customWidth="1" min="10" max="10" width="21.71"/>
+    <col customWidth="1" min="11" max="11" width="27.71"/>
+    <col customWidth="1" min="12" max="12" width="32.43"/>
+    <col customWidth="1" min="13" max="13" width="30.29"/>
+    <col customWidth="1" min="14" max="14" width="16.14"/>
+    <col customWidth="1" min="15" max="16" width="17.86"/>
+    <col customWidth="1" min="17" max="17" width="17.57"/>
+    <col customWidth="1" min="18" max="18" width="14.29"/>
+    <col customWidth="1" min="19" max="19" width="22.86"/>
+    <col customWidth="1" min="20" max="20" width="16.14"/>
+    <col customWidth="1" min="21" max="21" width="21.86"/>
+    <col customWidth="1" min="22" max="22" width="18.14"/>
+    <col customWidth="1" min="23" max="23" width="20.43"/>
+    <col customWidth="1" min="24" max="24" width="8.86"/>
+    <col customWidth="1" min="25" max="25" width="17.29"/>
+    <col customWidth="1" min="26" max="26" width="13.14"/>
+    <col customWidth="1" min="27" max="27" width="21.71"/>
+    <col customWidth="1" min="28" max="28" width="23.29"/>
+    <col customWidth="1" min="29" max="29" width="24.71"/>
+    <col customWidth="1" min="30" max="30" width="21.14"/>
+    <col customWidth="1" min="31" max="32" width="21.0"/>
+    <col customWidth="1" min="33" max="33" width="21.57"/>
+    <col customWidth="1" min="34" max="34" width="24.57"/>
+    <col customWidth="1" min="35" max="35" width="21.86"/>
+    <col customWidth="1" min="36" max="43" width="24.86"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:32">
+    <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1527,7 +596,7 @@
       <c r="AE1" s="2"/>
       <c r="AF1" s="2"/>
     </row>
-    <row r="2" ht="14.25" customHeight="1" spans="1:43">
+    <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1600,7 +669,7 @@
       <c r="X2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Y2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Z2" s="1" t="s">
@@ -1634,7 +703,7 @@
       <c r="AJ2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="4" t="s">
+      <c r="AK2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="AL2" s="1" t="s">
@@ -1646,146 +715,146 @@
       <c r="AN2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AO2" s="4" t="s">
+      <c r="AO2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="AP2" s="4"/>
+      <c r="AP2" s="5"/>
       <c r="AQ2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1" spans="1:43">
+    <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="B3" s="3">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="C3" s="3">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="D3" s="3">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="E3" s="3">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="F3" s="3">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="G3" s="3">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="H3" s="3">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="I3" s="3">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="J3" s="3">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="K3" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="L3" s="3">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="M3" s="3">
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="N3" s="3">
-        <v>13</v>
+        <v>13.0</v>
       </c>
       <c r="O3" s="3">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="P3" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="Q3" s="3">
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="R3" s="3">
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="S3" s="3">
-        <v>18</v>
+        <v>18.0</v>
       </c>
       <c r="T3" s="3">
-        <v>19</v>
+        <v>19.0</v>
       </c>
       <c r="U3" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="V3" s="3">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="W3" s="3">
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="X3" s="3">
-        <v>23</v>
-      </c>
-      <c r="Y3" s="5">
-        <v>24</v>
-      </c>
-      <c r="Z3" s="5">
-        <v>25</v>
-      </c>
-      <c r="AA3" s="5">
-        <v>26</v>
-      </c>
-      <c r="AB3" s="5">
-        <v>27</v>
-      </c>
-      <c r="AC3" s="5">
-        <v>28</v>
-      </c>
-      <c r="AD3" s="5">
-        <v>29</v>
-      </c>
-      <c r="AE3" s="5">
-        <v>30</v>
-      </c>
-      <c r="AF3" s="5">
-        <v>31</v>
-      </c>
-      <c r="AG3" s="5">
-        <v>32</v>
-      </c>
-      <c r="AH3" s="5">
-        <v>33</v>
-      </c>
-      <c r="AI3" s="5">
-        <v>34</v>
-      </c>
-      <c r="AJ3" s="5">
-        <v>35</v>
-      </c>
-      <c r="AK3" s="5">
-        <v>36</v>
-      </c>
-      <c r="AL3" s="5">
-        <v>37</v>
-      </c>
-      <c r="AM3" s="5">
-        <v>38</v>
-      </c>
-      <c r="AN3" s="5">
-        <v>39</v>
-      </c>
-      <c r="AO3" s="5">
-        <v>40</v>
-      </c>
-      <c r="AP3" s="5">
-        <v>41</v>
-      </c>
-      <c r="AQ3" s="5">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1" spans="1:43">
+        <v>23.0</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>24.0</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>25.0</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>26.0</v>
+      </c>
+      <c r="AB3" s="4">
+        <v>27.0</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>28.0</v>
+      </c>
+      <c r="AD3" s="4">
+        <v>29.0</v>
+      </c>
+      <c r="AE3" s="4">
+        <v>30.0</v>
+      </c>
+      <c r="AF3" s="4">
+        <v>31.0</v>
+      </c>
+      <c r="AG3" s="4">
+        <v>32.0</v>
+      </c>
+      <c r="AH3" s="4">
+        <v>33.0</v>
+      </c>
+      <c r="AI3" s="4">
+        <v>34.0</v>
+      </c>
+      <c r="AJ3" s="4">
+        <v>35.0</v>
+      </c>
+      <c r="AK3" s="4">
+        <v>36.0</v>
+      </c>
+      <c r="AL3" s="4">
+        <v>37.0</v>
+      </c>
+      <c r="AM3" s="4">
+        <v>38.0</v>
+      </c>
+      <c r="AN3" s="4">
+        <v>39.0</v>
+      </c>
+      <c r="AO3" s="4">
+        <v>40.0</v>
+      </c>
+      <c r="AP3" s="4">
+        <v>41.0</v>
+      </c>
+      <c r="AQ3" s="4">
+        <v>42.0</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1858,7 +927,7 @@
       <c r="X4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Y4" s="4" t="s">
         <v>27</v>
       </c>
       <c r="Z4" s="1" t="s">
@@ -1894,7 +963,7 @@
       <c r="AJ4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AK4" s="4" t="s">
+      <c r="AK4" s="5" t="s">
         <v>39</v>
       </c>
       <c r="AL4" s="1" t="s">
@@ -1906,24 +975,24 @@
       <c r="AN4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AO4" s="4" t="s">
+      <c r="AO4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AP4" s="4" t="s">
+      <c r="AP4" s="5" t="s">
         <v>44</v>
       </c>
       <c r="AQ4" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1" spans="1:43">
+    <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1989,7 +1058,7 @@
       <c r="X5" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Y5" s="4" t="s">
         <v>70</v>
       </c>
       <c r="Z5" s="1" t="s">
@@ -2025,29 +1094,29 @@
       <c r="AJ5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AK5" s="5" t="s">
+      <c r="AK5" s="4" t="s">
         <v>81</v>
       </c>
       <c r="AL5" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="AM5" s="5" t="s">
+      <c r="AM5" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AN5" s="5" t="s">
+      <c r="AN5" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AO5" s="5" t="s">
+      <c r="AO5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="AP5" s="5" t="s">
+      <c r="AP5" s="4" t="s">
         <v>86</v>
       </c>
       <c r="AQ5" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1" spans="2:32">
+    <row r="6" ht="14.25" customHeight="1">
       <c r="B6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="3"/>
@@ -2058,7 +1127,7 @@
       <c r="AE6" s="2"/>
       <c r="AF6" s="2"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1" spans="2:32">
+    <row r="7" ht="14.25" customHeight="1">
       <c r="B7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="3"/>
@@ -2069,7 +1138,7 @@
       <c r="AE7" s="2"/>
       <c r="AF7" s="2"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1" spans="2:32">
+    <row r="8" ht="14.25" customHeight="1">
       <c r="B8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="3"/>
@@ -2080,7 +1149,7 @@
       <c r="AE8" s="2"/>
       <c r="AF8" s="2"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1" spans="2:32">
+    <row r="9" ht="14.25" customHeight="1">
       <c r="B9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="3"/>
@@ -2091,7 +1160,7 @@
       <c r="AE9" s="2"/>
       <c r="AF9" s="2"/>
     </row>
-    <row r="10" ht="14.25" customHeight="1" spans="2:32">
+    <row r="10" ht="14.25" customHeight="1">
       <c r="B10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="3"/>
@@ -2102,7 +1171,7 @@
       <c r="AE10" s="2"/>
       <c r="AF10" s="2"/>
     </row>
-    <row r="11" ht="14.25" customHeight="1" spans="2:32">
+    <row r="11" ht="14.25" customHeight="1">
       <c r="B11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="3"/>
@@ -2113,7 +1182,7 @@
       <c r="AE11" s="2"/>
       <c r="AF11" s="2"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1" spans="2:32">
+    <row r="12" ht="14.25" customHeight="1">
       <c r="B12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="3"/>
@@ -2124,7 +1193,7 @@
       <c r="AE12" s="2"/>
       <c r="AF12" s="2"/>
     </row>
-    <row r="13" ht="14.25" customHeight="1" spans="2:32">
+    <row r="13" ht="14.25" customHeight="1">
       <c r="B13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="3"/>
@@ -2135,7 +1204,7 @@
       <c r="AE13" s="2"/>
       <c r="AF13" s="2"/>
     </row>
-    <row r="14" ht="14.25" customHeight="1" spans="2:32">
+    <row r="14" ht="14.25" customHeight="1">
       <c r="B14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="3"/>
@@ -2146,7 +1215,7 @@
       <c r="AE14" s="2"/>
       <c r="AF14" s="2"/>
     </row>
-    <row r="15" ht="14.25" customHeight="1" spans="2:32">
+    <row r="15" ht="14.25" customHeight="1">
       <c r="B15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="3"/>
@@ -2157,7 +1226,7 @@
       <c r="AE15" s="2"/>
       <c r="AF15" s="2"/>
     </row>
-    <row r="16" ht="14.25" customHeight="1" spans="2:32">
+    <row r="16" ht="14.25" customHeight="1">
       <c r="B16" s="2"/>
       <c r="T16" s="2"/>
       <c r="U16" s="3"/>
@@ -2168,7 +1237,7 @@
       <c r="AE16" s="2"/>
       <c r="AF16" s="2"/>
     </row>
-    <row r="17" ht="14.25" customHeight="1" spans="2:32">
+    <row r="17" ht="14.25" customHeight="1">
       <c r="B17" s="2"/>
       <c r="T17" s="2"/>
       <c r="U17" s="3"/>
@@ -2179,7 +1248,7 @@
       <c r="AE17" s="2"/>
       <c r="AF17" s="2"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1" spans="2:32">
+    <row r="18" ht="14.25" customHeight="1">
       <c r="B18" s="2"/>
       <c r="T18" s="2"/>
       <c r="U18" s="3"/>
@@ -2190,7 +1259,7 @@
       <c r="AE18" s="2"/>
       <c r="AF18" s="2"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1" spans="2:32">
+    <row r="19" ht="14.25" customHeight="1">
       <c r="B19" s="2"/>
       <c r="T19" s="2"/>
       <c r="U19" s="3"/>
@@ -2201,7 +1270,7 @@
       <c r="AE19" s="2"/>
       <c r="AF19" s="2"/>
     </row>
-    <row r="20" ht="14.25" customHeight="1" spans="2:32">
+    <row r="20" ht="14.25" customHeight="1">
       <c r="B20" s="2"/>
       <c r="T20" s="2"/>
       <c r="U20" s="3"/>
@@ -2212,7 +1281,7 @@
       <c r="AE20" s="2"/>
       <c r="AF20" s="2"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1" spans="2:32">
+    <row r="21" ht="14.25" customHeight="1">
       <c r="B21" s="2"/>
       <c r="T21" s="2"/>
       <c r="U21" s="3"/>
@@ -2223,7 +1292,7 @@
       <c r="AE21" s="2"/>
       <c r="AF21" s="2"/>
     </row>
-    <row r="22" ht="14.25" customHeight="1" spans="2:32">
+    <row r="22" ht="14.25" customHeight="1">
       <c r="B22" s="2"/>
       <c r="T22" s="2"/>
       <c r="U22" s="3"/>
@@ -2234,7 +1303,7 @@
       <c r="AE22" s="2"/>
       <c r="AF22" s="2"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1" spans="2:32">
+    <row r="23" ht="14.25" customHeight="1">
       <c r="B23" s="2"/>
       <c r="T23" s="2"/>
       <c r="U23" s="3"/>
@@ -2245,7 +1314,7 @@
       <c r="AE23" s="2"/>
       <c r="AF23" s="2"/>
     </row>
-    <row r="24" ht="14.25" customHeight="1" spans="2:32">
+    <row r="24" ht="14.25" customHeight="1">
       <c r="B24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="3"/>
@@ -2256,7 +1325,7 @@
       <c r="AE24" s="2"/>
       <c r="AF24" s="2"/>
     </row>
-    <row r="25" ht="14.25" customHeight="1" spans="2:32">
+    <row r="25" ht="14.25" customHeight="1">
       <c r="B25" s="2"/>
       <c r="T25" s="2"/>
       <c r="U25" s="3"/>
@@ -2267,7 +1336,7 @@
       <c r="AE25" s="2"/>
       <c r="AF25" s="2"/>
     </row>
-    <row r="26" ht="14.25" customHeight="1" spans="2:32">
+    <row r="26" ht="14.25" customHeight="1">
       <c r="B26" s="2"/>
       <c r="T26" s="2"/>
       <c r="U26" s="3"/>
@@ -2278,7 +1347,7 @@
       <c r="AE26" s="2"/>
       <c r="AF26" s="2"/>
     </row>
-    <row r="27" ht="14.25" customHeight="1" spans="2:32">
+    <row r="27" ht="14.25" customHeight="1">
       <c r="B27" s="2"/>
       <c r="T27" s="2"/>
       <c r="U27" s="3"/>
@@ -2289,7 +1358,7 @@
       <c r="AE27" s="2"/>
       <c r="AF27" s="2"/>
     </row>
-    <row r="28" ht="14.25" customHeight="1" spans="2:32">
+    <row r="28" ht="14.25" customHeight="1">
       <c r="B28" s="2"/>
       <c r="T28" s="2"/>
       <c r="U28" s="3"/>
@@ -2300,7 +1369,7 @@
       <c r="AE28" s="2"/>
       <c r="AF28" s="2"/>
     </row>
-    <row r="29" ht="14.25" customHeight="1" spans="2:32">
+    <row r="29" ht="14.25" customHeight="1">
       <c r="B29" s="2"/>
       <c r="T29" s="2"/>
       <c r="U29" s="3"/>
@@ -2311,7 +1380,7 @@
       <c r="AE29" s="2"/>
       <c r="AF29" s="2"/>
     </row>
-    <row r="30" ht="14.25" customHeight="1" spans="2:32">
+    <row r="30" ht="14.25" customHeight="1">
       <c r="B30" s="2"/>
       <c r="T30" s="2"/>
       <c r="U30" s="3"/>
@@ -2322,7 +1391,7 @@
       <c r="AE30" s="2"/>
       <c r="AF30" s="2"/>
     </row>
-    <row r="31" ht="14.25" customHeight="1" spans="2:32">
+    <row r="31" ht="14.25" customHeight="1">
       <c r="B31" s="2"/>
       <c r="T31" s="2"/>
       <c r="U31" s="3"/>
@@ -2333,7 +1402,7 @@
       <c r="AE31" s="2"/>
       <c r="AF31" s="2"/>
     </row>
-    <row r="32" ht="14.25" customHeight="1" spans="2:32">
+    <row r="32" ht="14.25" customHeight="1">
       <c r="B32" s="2"/>
       <c r="T32" s="2"/>
       <c r="U32" s="3"/>
@@ -2344,7 +1413,7 @@
       <c r="AE32" s="2"/>
       <c r="AF32" s="2"/>
     </row>
-    <row r="33" ht="14.25" customHeight="1" spans="2:32">
+    <row r="33" ht="14.25" customHeight="1">
       <c r="B33" s="2"/>
       <c r="T33" s="2"/>
       <c r="U33" s="3"/>
@@ -2355,7 +1424,7 @@
       <c r="AE33" s="2"/>
       <c r="AF33" s="2"/>
     </row>
-    <row r="34" ht="14.25" customHeight="1" spans="2:32">
+    <row r="34" ht="14.25" customHeight="1">
       <c r="B34" s="2"/>
       <c r="T34" s="2"/>
       <c r="U34" s="3"/>
@@ -2366,7 +1435,7 @@
       <c r="AE34" s="2"/>
       <c r="AF34" s="2"/>
     </row>
-    <row r="35" ht="14.25" customHeight="1" spans="2:32">
+    <row r="35" ht="14.25" customHeight="1">
       <c r="B35" s="2"/>
       <c r="T35" s="2"/>
       <c r="U35" s="3"/>
@@ -2377,7 +1446,7 @@
       <c r="AE35" s="2"/>
       <c r="AF35" s="2"/>
     </row>
-    <row r="36" ht="14.25" customHeight="1" spans="2:32">
+    <row r="36" ht="14.25" customHeight="1">
       <c r="B36" s="2"/>
       <c r="T36" s="2"/>
       <c r="U36" s="3"/>
@@ -2388,7 +1457,7 @@
       <c r="AE36" s="2"/>
       <c r="AF36" s="2"/>
     </row>
-    <row r="37" ht="14.25" customHeight="1" spans="2:32">
+    <row r="37" ht="14.25" customHeight="1">
       <c r="B37" s="2"/>
       <c r="T37" s="2"/>
       <c r="U37" s="3"/>
@@ -2399,7 +1468,7 @@
       <c r="AE37" s="2"/>
       <c r="AF37" s="2"/>
     </row>
-    <row r="38" ht="14.25" customHeight="1" spans="2:32">
+    <row r="38" ht="14.25" customHeight="1">
       <c r="B38" s="2"/>
       <c r="T38" s="2"/>
       <c r="U38" s="3"/>
@@ -2410,7 +1479,7 @@
       <c r="AE38" s="2"/>
       <c r="AF38" s="2"/>
     </row>
-    <row r="39" ht="14.25" customHeight="1" spans="2:32">
+    <row r="39" ht="14.25" customHeight="1">
       <c r="B39" s="2"/>
       <c r="T39" s="2"/>
       <c r="U39" s="3"/>
@@ -2421,7 +1490,7 @@
       <c r="AE39" s="2"/>
       <c r="AF39" s="2"/>
     </row>
-    <row r="40" ht="14.25" customHeight="1" spans="2:32">
+    <row r="40" ht="14.25" customHeight="1">
       <c r="B40" s="2"/>
       <c r="T40" s="2"/>
       <c r="U40" s="3"/>
@@ -2432,7 +1501,7 @@
       <c r="AE40" s="2"/>
       <c r="AF40" s="2"/>
     </row>
-    <row r="41" ht="14.25" customHeight="1" spans="2:32">
+    <row r="41" ht="14.25" customHeight="1">
       <c r="B41" s="2"/>
       <c r="T41" s="2"/>
       <c r="U41" s="3"/>
@@ -2443,7 +1512,7 @@
       <c r="AE41" s="2"/>
       <c r="AF41" s="2"/>
     </row>
-    <row r="42" ht="14.25" customHeight="1" spans="2:32">
+    <row r="42" ht="14.25" customHeight="1">
       <c r="B42" s="2"/>
       <c r="T42" s="2"/>
       <c r="U42" s="3"/>
@@ -2454,7 +1523,7 @@
       <c r="AE42" s="2"/>
       <c r="AF42" s="2"/>
     </row>
-    <row r="43" ht="14.25" customHeight="1" spans="2:32">
+    <row r="43" ht="14.25" customHeight="1">
       <c r="B43" s="2"/>
       <c r="T43" s="2"/>
       <c r="U43" s="3"/>
@@ -2465,7 +1534,7 @@
       <c r="AE43" s="2"/>
       <c r="AF43" s="2"/>
     </row>
-    <row r="44" ht="14.25" customHeight="1" spans="2:32">
+    <row r="44" ht="14.25" customHeight="1">
       <c r="B44" s="2"/>
       <c r="T44" s="2"/>
       <c r="U44" s="3"/>
@@ -2476,7 +1545,7 @@
       <c r="AE44" s="2"/>
       <c r="AF44" s="2"/>
     </row>
-    <row r="45" ht="14.25" customHeight="1" spans="2:32">
+    <row r="45" ht="14.25" customHeight="1">
       <c r="B45" s="2"/>
       <c r="T45" s="2"/>
       <c r="U45" s="3"/>
@@ -2487,7 +1556,7 @@
       <c r="AE45" s="2"/>
       <c r="AF45" s="2"/>
     </row>
-    <row r="46" ht="14.25" customHeight="1" spans="2:32">
+    <row r="46" ht="14.25" customHeight="1">
       <c r="B46" s="2"/>
       <c r="T46" s="2"/>
       <c r="U46" s="3"/>
@@ -2498,7 +1567,7 @@
       <c r="AE46" s="2"/>
       <c r="AF46" s="2"/>
     </row>
-    <row r="47" ht="14.25" customHeight="1" spans="2:32">
+    <row r="47" ht="14.25" customHeight="1">
       <c r="B47" s="2"/>
       <c r="T47" s="2"/>
       <c r="U47" s="3"/>
@@ -2509,7 +1578,7 @@
       <c r="AE47" s="2"/>
       <c r="AF47" s="2"/>
     </row>
-    <row r="48" ht="14.25" customHeight="1" spans="2:32">
+    <row r="48" ht="14.25" customHeight="1">
       <c r="B48" s="2"/>
       <c r="T48" s="2"/>
       <c r="U48" s="3"/>
@@ -2520,7 +1589,7 @@
       <c r="AE48" s="2"/>
       <c r="AF48" s="2"/>
     </row>
-    <row r="49" ht="14.25" customHeight="1" spans="2:32">
+    <row r="49" ht="14.25" customHeight="1">
       <c r="B49" s="2"/>
       <c r="T49" s="2"/>
       <c r="U49" s="3"/>
@@ -2531,7 +1600,7 @@
       <c r="AE49" s="2"/>
       <c r="AF49" s="2"/>
     </row>
-    <row r="50" ht="14.25" customHeight="1" spans="2:32">
+    <row r="50" ht="14.25" customHeight="1">
       <c r="B50" s="2"/>
       <c r="T50" s="2"/>
       <c r="U50" s="3"/>
@@ -2542,7 +1611,7 @@
       <c r="AE50" s="2"/>
       <c r="AF50" s="2"/>
     </row>
-    <row r="51" ht="14.25" customHeight="1" spans="2:32">
+    <row r="51" ht="14.25" customHeight="1">
       <c r="B51" s="2"/>
       <c r="T51" s="2"/>
       <c r="U51" s="3"/>
@@ -2553,7 +1622,7 @@
       <c r="AE51" s="2"/>
       <c r="AF51" s="2"/>
     </row>
-    <row r="52" ht="14.25" customHeight="1" spans="2:32">
+    <row r="52" ht="14.25" customHeight="1">
       <c r="B52" s="2"/>
       <c r="T52" s="2"/>
       <c r="U52" s="3"/>
@@ -2564,7 +1633,7 @@
       <c r="AE52" s="2"/>
       <c r="AF52" s="2"/>
     </row>
-    <row r="53" ht="14.25" customHeight="1" spans="2:32">
+    <row r="53" ht="14.25" customHeight="1">
       <c r="B53" s="2"/>
       <c r="T53" s="2"/>
       <c r="U53" s="3"/>
@@ -2575,7 +1644,7 @@
       <c r="AE53" s="2"/>
       <c r="AF53" s="2"/>
     </row>
-    <row r="54" ht="14.25" customHeight="1" spans="2:32">
+    <row r="54" ht="14.25" customHeight="1">
       <c r="B54" s="2"/>
       <c r="T54" s="2"/>
       <c r="U54" s="3"/>
@@ -2586,7 +1655,7 @@
       <c r="AE54" s="2"/>
       <c r="AF54" s="2"/>
     </row>
-    <row r="55" ht="14.25" customHeight="1" spans="2:32">
+    <row r="55" ht="14.25" customHeight="1">
       <c r="B55" s="2"/>
       <c r="T55" s="2"/>
       <c r="U55" s="3"/>
@@ -2597,7 +1666,7 @@
       <c r="AE55" s="2"/>
       <c r="AF55" s="2"/>
     </row>
-    <row r="56" ht="14.25" customHeight="1" spans="2:32">
+    <row r="56" ht="14.25" customHeight="1">
       <c r="B56" s="2"/>
       <c r="T56" s="2"/>
       <c r="U56" s="3"/>
@@ -2608,7 +1677,7 @@
       <c r="AE56" s="2"/>
       <c r="AF56" s="2"/>
     </row>
-    <row r="57" ht="14.25" customHeight="1" spans="2:32">
+    <row r="57" ht="14.25" customHeight="1">
       <c r="B57" s="2"/>
       <c r="T57" s="2"/>
       <c r="U57" s="3"/>
@@ -2619,7 +1688,7 @@
       <c r="AE57" s="2"/>
       <c r="AF57" s="2"/>
     </row>
-    <row r="58" ht="14.25" customHeight="1" spans="2:32">
+    <row r="58" ht="14.25" customHeight="1">
       <c r="B58" s="2"/>
       <c r="T58" s="2"/>
       <c r="U58" s="3"/>
@@ -2630,7 +1699,7 @@
       <c r="AE58" s="2"/>
       <c r="AF58" s="2"/>
     </row>
-    <row r="59" ht="14.25" customHeight="1" spans="2:32">
+    <row r="59" ht="14.25" customHeight="1">
       <c r="B59" s="2"/>
       <c r="T59" s="2"/>
       <c r="U59" s="3"/>
@@ -2641,7 +1710,7 @@
       <c r="AE59" s="2"/>
       <c r="AF59" s="2"/>
     </row>
-    <row r="60" ht="14.25" customHeight="1" spans="2:32">
+    <row r="60" ht="14.25" customHeight="1">
       <c r="B60" s="2"/>
       <c r="T60" s="2"/>
       <c r="U60" s="3"/>
@@ -2652,7 +1721,7 @@
       <c r="AE60" s="2"/>
       <c r="AF60" s="2"/>
     </row>
-    <row r="61" ht="14.25" customHeight="1" spans="2:32">
+    <row r="61" ht="14.25" customHeight="1">
       <c r="B61" s="2"/>
       <c r="T61" s="2"/>
       <c r="U61" s="3"/>
@@ -2663,7 +1732,7 @@
       <c r="AE61" s="2"/>
       <c r="AF61" s="2"/>
     </row>
-    <row r="62" ht="14.25" customHeight="1" spans="2:32">
+    <row r="62" ht="14.25" customHeight="1">
       <c r="B62" s="2"/>
       <c r="T62" s="2"/>
       <c r="U62" s="3"/>
@@ -2674,7 +1743,7 @@
       <c r="AE62" s="2"/>
       <c r="AF62" s="2"/>
     </row>
-    <row r="63" ht="14.25" customHeight="1" spans="2:32">
+    <row r="63" ht="14.25" customHeight="1">
       <c r="B63" s="2"/>
       <c r="T63" s="2"/>
       <c r="U63" s="3"/>
@@ -2685,7 +1754,7 @@
       <c r="AE63" s="2"/>
       <c r="AF63" s="2"/>
     </row>
-    <row r="64" ht="14.25" customHeight="1" spans="2:32">
+    <row r="64" ht="14.25" customHeight="1">
       <c r="B64" s="2"/>
       <c r="T64" s="2"/>
       <c r="U64" s="3"/>
@@ -2696,7 +1765,7 @@
       <c r="AE64" s="2"/>
       <c r="AF64" s="2"/>
     </row>
-    <row r="65" ht="14.25" customHeight="1" spans="2:32">
+    <row r="65" ht="14.25" customHeight="1">
       <c r="B65" s="2"/>
       <c r="T65" s="2"/>
       <c r="U65" s="3"/>
@@ -2707,7 +1776,7 @@
       <c r="AE65" s="2"/>
       <c r="AF65" s="2"/>
     </row>
-    <row r="66" ht="14.25" customHeight="1" spans="2:32">
+    <row r="66" ht="14.25" customHeight="1">
       <c r="B66" s="2"/>
       <c r="T66" s="2"/>
       <c r="U66" s="3"/>
@@ -2718,7 +1787,7 @@
       <c r="AE66" s="2"/>
       <c r="AF66" s="2"/>
     </row>
-    <row r="67" ht="14.25" customHeight="1" spans="2:32">
+    <row r="67" ht="14.25" customHeight="1">
       <c r="B67" s="2"/>
       <c r="T67" s="2"/>
       <c r="U67" s="3"/>
@@ -2729,7 +1798,7 @@
       <c r="AE67" s="2"/>
       <c r="AF67" s="2"/>
     </row>
-    <row r="68" ht="14.25" customHeight="1" spans="2:32">
+    <row r="68" ht="14.25" customHeight="1">
       <c r="B68" s="2"/>
       <c r="T68" s="2"/>
       <c r="U68" s="3"/>
@@ -2740,7 +1809,7 @@
       <c r="AE68" s="2"/>
       <c r="AF68" s="2"/>
     </row>
-    <row r="69" ht="14.25" customHeight="1" spans="2:32">
+    <row r="69" ht="14.25" customHeight="1">
       <c r="B69" s="2"/>
       <c r="T69" s="2"/>
       <c r="U69" s="3"/>
@@ -2751,7 +1820,7 @@
       <c r="AE69" s="2"/>
       <c r="AF69" s="2"/>
     </row>
-    <row r="70" ht="14.25" customHeight="1" spans="2:32">
+    <row r="70" ht="14.25" customHeight="1">
       <c r="B70" s="2"/>
       <c r="T70" s="2"/>
       <c r="U70" s="3"/>
@@ -2762,7 +1831,7 @@
       <c r="AE70" s="2"/>
       <c r="AF70" s="2"/>
     </row>
-    <row r="71" ht="14.25" customHeight="1" spans="2:32">
+    <row r="71" ht="14.25" customHeight="1">
       <c r="B71" s="2"/>
       <c r="T71" s="2"/>
       <c r="U71" s="3"/>
@@ -2773,7 +1842,7 @@
       <c r="AE71" s="2"/>
       <c r="AF71" s="2"/>
     </row>
-    <row r="72" ht="14.25" customHeight="1" spans="2:32">
+    <row r="72" ht="14.25" customHeight="1">
       <c r="B72" s="2"/>
       <c r="T72" s="2"/>
       <c r="U72" s="3"/>
@@ -2784,7 +1853,7 @@
       <c r="AE72" s="2"/>
       <c r="AF72" s="2"/>
     </row>
-    <row r="73" ht="14.25" customHeight="1" spans="2:32">
+    <row r="73" ht="14.25" customHeight="1">
       <c r="B73" s="2"/>
       <c r="T73" s="2"/>
       <c r="U73" s="3"/>
@@ -2795,7 +1864,7 @@
       <c r="AE73" s="2"/>
       <c r="AF73" s="2"/>
     </row>
-    <row r="74" ht="14.25" customHeight="1" spans="2:32">
+    <row r="74" ht="14.25" customHeight="1">
       <c r="B74" s="2"/>
       <c r="T74" s="2"/>
       <c r="U74" s="3"/>
@@ -2806,7 +1875,7 @@
       <c r="AE74" s="2"/>
       <c r="AF74" s="2"/>
     </row>
-    <row r="75" ht="14.25" customHeight="1" spans="2:32">
+    <row r="75" ht="14.25" customHeight="1">
       <c r="B75" s="2"/>
       <c r="T75" s="2"/>
       <c r="U75" s="3"/>
@@ -2817,7 +1886,7 @@
       <c r="AE75" s="2"/>
       <c r="AF75" s="2"/>
     </row>
-    <row r="76" ht="14.25" customHeight="1" spans="2:32">
+    <row r="76" ht="14.25" customHeight="1">
       <c r="B76" s="2"/>
       <c r="T76" s="2"/>
       <c r="U76" s="3"/>
@@ -2828,7 +1897,7 @@
       <c r="AE76" s="2"/>
       <c r="AF76" s="2"/>
     </row>
-    <row r="77" ht="14.25" customHeight="1" spans="2:32">
+    <row r="77" ht="14.25" customHeight="1">
       <c r="B77" s="2"/>
       <c r="T77" s="2"/>
       <c r="U77" s="3"/>
@@ -2839,7 +1908,7 @@
       <c r="AE77" s="2"/>
       <c r="AF77" s="2"/>
     </row>
-    <row r="78" ht="14.25" customHeight="1" spans="2:32">
+    <row r="78" ht="14.25" customHeight="1">
       <c r="B78" s="2"/>
       <c r="T78" s="2"/>
       <c r="U78" s="3"/>
@@ -2850,7 +1919,7 @@
       <c r="AE78" s="2"/>
       <c r="AF78" s="2"/>
     </row>
-    <row r="79" ht="14.25" customHeight="1" spans="2:32">
+    <row r="79" ht="14.25" customHeight="1">
       <c r="B79" s="2"/>
       <c r="T79" s="2"/>
       <c r="U79" s="3"/>
@@ -2861,7 +1930,7 @@
       <c r="AE79" s="2"/>
       <c r="AF79" s="2"/>
     </row>
-    <row r="80" ht="14.25" customHeight="1" spans="2:32">
+    <row r="80" ht="14.25" customHeight="1">
       <c r="B80" s="2"/>
       <c r="T80" s="2"/>
       <c r="U80" s="3"/>
@@ -2872,7 +1941,7 @@
       <c r="AE80" s="2"/>
       <c r="AF80" s="2"/>
     </row>
-    <row r="81" ht="14.25" customHeight="1" spans="2:32">
+    <row r="81" ht="14.25" customHeight="1">
       <c r="B81" s="2"/>
       <c r="T81" s="2"/>
       <c r="U81" s="3"/>
@@ -2883,7 +1952,7 @@
       <c r="AE81" s="2"/>
       <c r="AF81" s="2"/>
     </row>
-    <row r="82" ht="14.25" customHeight="1" spans="2:32">
+    <row r="82" ht="14.25" customHeight="1">
       <c r="B82" s="2"/>
       <c r="T82" s="2"/>
       <c r="U82" s="3"/>
@@ -2894,7 +1963,7 @@
       <c r="AE82" s="2"/>
       <c r="AF82" s="2"/>
     </row>
-    <row r="83" ht="14.25" customHeight="1" spans="2:32">
+    <row r="83" ht="14.25" customHeight="1">
       <c r="B83" s="2"/>
       <c r="T83" s="2"/>
       <c r="U83" s="3"/>
@@ -2905,7 +1974,7 @@
       <c r="AE83" s="2"/>
       <c r="AF83" s="2"/>
     </row>
-    <row r="84" ht="14.25" customHeight="1" spans="2:32">
+    <row r="84" ht="14.25" customHeight="1">
       <c r="B84" s="2"/>
       <c r="T84" s="2"/>
       <c r="U84" s="3"/>
@@ -2916,7 +1985,7 @@
       <c r="AE84" s="2"/>
       <c r="AF84" s="2"/>
     </row>
-    <row r="85" ht="14.25" customHeight="1" spans="2:32">
+    <row r="85" ht="14.25" customHeight="1">
       <c r="B85" s="2"/>
       <c r="T85" s="2"/>
       <c r="U85" s="3"/>
@@ -2927,7 +1996,7 @@
       <c r="AE85" s="2"/>
       <c r="AF85" s="2"/>
     </row>
-    <row r="86" ht="14.25" customHeight="1" spans="2:32">
+    <row r="86" ht="14.25" customHeight="1">
       <c r="B86" s="2"/>
       <c r="T86" s="2"/>
       <c r="U86" s="3"/>
@@ -2938,7 +2007,7 @@
       <c r="AE86" s="2"/>
       <c r="AF86" s="2"/>
     </row>
-    <row r="87" ht="14.25" customHeight="1" spans="2:32">
+    <row r="87" ht="14.25" customHeight="1">
       <c r="B87" s="2"/>
       <c r="T87" s="2"/>
       <c r="U87" s="3"/>
@@ -2949,7 +2018,7 @@
       <c r="AE87" s="2"/>
       <c r="AF87" s="2"/>
     </row>
-    <row r="88" ht="14.25" customHeight="1" spans="2:32">
+    <row r="88" ht="14.25" customHeight="1">
       <c r="B88" s="2"/>
       <c r="T88" s="2"/>
       <c r="U88" s="3"/>
@@ -2960,7 +2029,7 @@
       <c r="AE88" s="2"/>
       <c r="AF88" s="2"/>
     </row>
-    <row r="89" ht="14.25" customHeight="1" spans="2:32">
+    <row r="89" ht="14.25" customHeight="1">
       <c r="B89" s="2"/>
       <c r="T89" s="2"/>
       <c r="U89" s="3"/>
@@ -2971,7 +2040,7 @@
       <c r="AE89" s="2"/>
       <c r="AF89" s="2"/>
     </row>
-    <row r="90" ht="14.25" customHeight="1" spans="2:32">
+    <row r="90" ht="14.25" customHeight="1">
       <c r="B90" s="2"/>
       <c r="T90" s="2"/>
       <c r="U90" s="3"/>
@@ -2982,7 +2051,7 @@
       <c r="AE90" s="2"/>
       <c r="AF90" s="2"/>
     </row>
-    <row r="91" ht="14.25" customHeight="1" spans="2:32">
+    <row r="91" ht="14.25" customHeight="1">
       <c r="B91" s="2"/>
       <c r="T91" s="2"/>
       <c r="U91" s="3"/>
@@ -2993,7 +2062,7 @@
       <c r="AE91" s="2"/>
       <c r="AF91" s="2"/>
     </row>
-    <row r="92" ht="14.25" customHeight="1" spans="2:32">
+    <row r="92" ht="14.25" customHeight="1">
       <c r="B92" s="2"/>
       <c r="T92" s="2"/>
       <c r="U92" s="3"/>
@@ -3004,7 +2073,7 @@
       <c r="AE92" s="2"/>
       <c r="AF92" s="2"/>
     </row>
-    <row r="93" ht="14.25" customHeight="1" spans="2:32">
+    <row r="93" ht="14.25" customHeight="1">
       <c r="B93" s="2"/>
       <c r="T93" s="2"/>
       <c r="U93" s="3"/>
@@ -3015,7 +2084,7 @@
       <c r="AE93" s="2"/>
       <c r="AF93" s="2"/>
     </row>
-    <row r="94" ht="14.25" customHeight="1" spans="2:32">
+    <row r="94" ht="14.25" customHeight="1">
       <c r="B94" s="2"/>
       <c r="T94" s="2"/>
       <c r="U94" s="3"/>
@@ -3026,7 +2095,7 @@
       <c r="AE94" s="2"/>
       <c r="AF94" s="2"/>
     </row>
-    <row r="95" ht="14.25" customHeight="1" spans="2:32">
+    <row r="95" ht="14.25" customHeight="1">
       <c r="B95" s="2"/>
       <c r="T95" s="2"/>
       <c r="U95" s="3"/>
@@ -3037,7 +2106,7 @@
       <c r="AE95" s="2"/>
       <c r="AF95" s="2"/>
     </row>
-    <row r="96" ht="14.25" customHeight="1" spans="2:32">
+    <row r="96" ht="14.25" customHeight="1">
       <c r="B96" s="2"/>
       <c r="T96" s="2"/>
       <c r="U96" s="3"/>
@@ -3048,7 +2117,7 @@
       <c r="AE96" s="2"/>
       <c r="AF96" s="2"/>
     </row>
-    <row r="97" ht="14.25" customHeight="1" spans="2:32">
+    <row r="97" ht="14.25" customHeight="1">
       <c r="B97" s="2"/>
       <c r="T97" s="2"/>
       <c r="U97" s="3"/>
@@ -3059,7 +2128,7 @@
       <c r="AE97" s="2"/>
       <c r="AF97" s="2"/>
     </row>
-    <row r="98" ht="14.25" customHeight="1" spans="2:32">
+    <row r="98" ht="14.25" customHeight="1">
       <c r="B98" s="2"/>
       <c r="T98" s="2"/>
       <c r="U98" s="3"/>
@@ -3070,7 +2139,7 @@
       <c r="AE98" s="2"/>
       <c r="AF98" s="2"/>
     </row>
-    <row r="99" ht="14.25" customHeight="1" spans="2:32">
+    <row r="99" ht="14.25" customHeight="1">
       <c r="B99" s="2"/>
       <c r="T99" s="2"/>
       <c r="U99" s="3"/>
@@ -3081,7 +2150,7 @@
       <c r="AE99" s="2"/>
       <c r="AF99" s="2"/>
     </row>
-    <row r="100" ht="14.25" customHeight="1" spans="2:32">
+    <row r="100" ht="14.25" customHeight="1">
       <c r="B100" s="2"/>
       <c r="T100" s="2"/>
       <c r="U100" s="3"/>
@@ -3092,7 +2161,7 @@
       <c r="AE100" s="2"/>
       <c r="AF100" s="2"/>
     </row>
-    <row r="101" ht="14.25" customHeight="1" spans="2:32">
+    <row r="101" ht="14.25" customHeight="1">
       <c r="B101" s="2"/>
       <c r="T101" s="2"/>
       <c r="U101" s="3"/>
@@ -3103,7 +2172,7 @@
       <c r="AE101" s="2"/>
       <c r="AF101" s="2"/>
     </row>
-    <row r="102" ht="14.25" customHeight="1" spans="2:32">
+    <row r="102" ht="14.25" customHeight="1">
       <c r="B102" s="2"/>
       <c r="T102" s="2"/>
       <c r="U102" s="3"/>
@@ -3114,7 +2183,7 @@
       <c r="AE102" s="2"/>
       <c r="AF102" s="2"/>
     </row>
-    <row r="103" ht="14.25" customHeight="1" spans="2:32">
+    <row r="103" ht="14.25" customHeight="1">
       <c r="B103" s="2"/>
       <c r="T103" s="2"/>
       <c r="U103" s="3"/>
@@ -3125,7 +2194,7 @@
       <c r="AE103" s="2"/>
       <c r="AF103" s="2"/>
     </row>
-    <row r="104" ht="14.25" customHeight="1" spans="2:32">
+    <row r="104" ht="14.25" customHeight="1">
       <c r="B104" s="2"/>
       <c r="T104" s="2"/>
       <c r="U104" s="3"/>
@@ -3136,7 +2205,7 @@
       <c r="AE104" s="2"/>
       <c r="AF104" s="2"/>
     </row>
-    <row r="105" ht="14.25" customHeight="1" spans="2:32">
+    <row r="105" ht="14.25" customHeight="1">
       <c r="B105" s="2"/>
       <c r="T105" s="2"/>
       <c r="U105" s="3"/>
@@ -3147,7 +2216,7 @@
       <c r="AE105" s="2"/>
       <c r="AF105" s="2"/>
     </row>
-    <row r="106" ht="14.25" customHeight="1" spans="2:32">
+    <row r="106" ht="14.25" customHeight="1">
       <c r="B106" s="2"/>
       <c r="T106" s="2"/>
       <c r="U106" s="3"/>
@@ -3158,7 +2227,7 @@
       <c r="AE106" s="2"/>
       <c r="AF106" s="2"/>
     </row>
-    <row r="107" ht="14.25" customHeight="1" spans="2:32">
+    <row r="107" ht="14.25" customHeight="1">
       <c r="B107" s="2"/>
       <c r="T107" s="2"/>
       <c r="U107" s="3"/>
@@ -3169,7 +2238,7 @@
       <c r="AE107" s="2"/>
       <c r="AF107" s="2"/>
     </row>
-    <row r="108" ht="14.25" customHeight="1" spans="2:32">
+    <row r="108" ht="14.25" customHeight="1">
       <c r="B108" s="2"/>
       <c r="T108" s="2"/>
       <c r="U108" s="3"/>
@@ -3180,7 +2249,7 @@
       <c r="AE108" s="2"/>
       <c r="AF108" s="2"/>
     </row>
-    <row r="109" ht="14.25" customHeight="1" spans="2:32">
+    <row r="109" ht="14.25" customHeight="1">
       <c r="B109" s="2"/>
       <c r="T109" s="2"/>
       <c r="U109" s="3"/>
@@ -3191,7 +2260,7 @@
       <c r="AE109" s="2"/>
       <c r="AF109" s="2"/>
     </row>
-    <row r="110" ht="14.25" customHeight="1" spans="2:32">
+    <row r="110" ht="14.25" customHeight="1">
       <c r="B110" s="2"/>
       <c r="T110" s="2"/>
       <c r="U110" s="3"/>
@@ -3202,7 +2271,7 @@
       <c r="AE110" s="2"/>
       <c r="AF110" s="2"/>
     </row>
-    <row r="111" ht="14.25" customHeight="1" spans="2:32">
+    <row r="111" ht="14.25" customHeight="1">
       <c r="B111" s="2"/>
       <c r="T111" s="2"/>
       <c r="U111" s="3"/>
@@ -3213,7 +2282,7 @@
       <c r="AE111" s="2"/>
       <c r="AF111" s="2"/>
     </row>
-    <row r="112" ht="14.25" customHeight="1" spans="2:32">
+    <row r="112" ht="14.25" customHeight="1">
       <c r="B112" s="2"/>
       <c r="T112" s="2"/>
       <c r="U112" s="3"/>
@@ -3224,7 +2293,7 @@
       <c r="AE112" s="2"/>
       <c r="AF112" s="2"/>
     </row>
-    <row r="113" ht="14.25" customHeight="1" spans="2:32">
+    <row r="113" ht="14.25" customHeight="1">
       <c r="B113" s="2"/>
       <c r="T113" s="2"/>
       <c r="U113" s="3"/>
@@ -3235,7 +2304,7 @@
       <c r="AE113" s="2"/>
       <c r="AF113" s="2"/>
     </row>
-    <row r="114" ht="14.25" customHeight="1" spans="2:32">
+    <row r="114" ht="14.25" customHeight="1">
       <c r="B114" s="2"/>
       <c r="T114" s="2"/>
       <c r="U114" s="3"/>
@@ -3246,7 +2315,7 @@
       <c r="AE114" s="2"/>
       <c r="AF114" s="2"/>
     </row>
-    <row r="115" ht="14.25" customHeight="1" spans="2:32">
+    <row r="115" ht="14.25" customHeight="1">
       <c r="B115" s="2"/>
       <c r="T115" s="2"/>
       <c r="U115" s="3"/>
@@ -3257,7 +2326,7 @@
       <c r="AE115" s="2"/>
       <c r="AF115" s="2"/>
     </row>
-    <row r="116" ht="14.25" customHeight="1" spans="2:32">
+    <row r="116" ht="14.25" customHeight="1">
       <c r="B116" s="2"/>
       <c r="T116" s="2"/>
       <c r="U116" s="3"/>
@@ -3268,7 +2337,7 @@
       <c r="AE116" s="2"/>
       <c r="AF116" s="2"/>
     </row>
-    <row r="117" ht="14.25" customHeight="1" spans="2:32">
+    <row r="117" ht="14.25" customHeight="1">
       <c r="B117" s="2"/>
       <c r="T117" s="2"/>
       <c r="U117" s="3"/>
@@ -3279,7 +2348,7 @@
       <c r="AE117" s="2"/>
       <c r="AF117" s="2"/>
     </row>
-    <row r="118" ht="14.25" customHeight="1" spans="2:32">
+    <row r="118" ht="14.25" customHeight="1">
       <c r="B118" s="2"/>
       <c r="T118" s="2"/>
       <c r="U118" s="3"/>
@@ -3290,7 +2359,7 @@
       <c r="AE118" s="2"/>
       <c r="AF118" s="2"/>
     </row>
-    <row r="119" ht="14.25" customHeight="1" spans="2:32">
+    <row r="119" ht="14.25" customHeight="1">
       <c r="B119" s="2"/>
       <c r="T119" s="2"/>
       <c r="U119" s="3"/>
@@ -3301,7 +2370,7 @@
       <c r="AE119" s="2"/>
       <c r="AF119" s="2"/>
     </row>
-    <row r="120" ht="14.25" customHeight="1" spans="2:32">
+    <row r="120" ht="14.25" customHeight="1">
       <c r="B120" s="2"/>
       <c r="T120" s="2"/>
       <c r="U120" s="3"/>
@@ -3312,7 +2381,7 @@
       <c r="AE120" s="2"/>
       <c r="AF120" s="2"/>
     </row>
-    <row r="121" ht="14.25" customHeight="1" spans="2:32">
+    <row r="121" ht="14.25" customHeight="1">
       <c r="B121" s="2"/>
       <c r="T121" s="2"/>
       <c r="U121" s="3"/>
@@ -3323,7 +2392,7 @@
       <c r="AE121" s="2"/>
       <c r="AF121" s="2"/>
     </row>
-    <row r="122" ht="14.25" customHeight="1" spans="2:32">
+    <row r="122" ht="14.25" customHeight="1">
       <c r="B122" s="2"/>
       <c r="T122" s="2"/>
       <c r="U122" s="3"/>
@@ -3334,7 +2403,7 @@
       <c r="AE122" s="2"/>
       <c r="AF122" s="2"/>
     </row>
-    <row r="123" ht="14.25" customHeight="1" spans="2:32">
+    <row r="123" ht="14.25" customHeight="1">
       <c r="B123" s="2"/>
       <c r="T123" s="2"/>
       <c r="U123" s="3"/>
@@ -3345,7 +2414,7 @@
       <c r="AE123" s="2"/>
       <c r="AF123" s="2"/>
     </row>
-    <row r="124" ht="14.25" customHeight="1" spans="2:32">
+    <row r="124" ht="14.25" customHeight="1">
       <c r="B124" s="2"/>
       <c r="T124" s="2"/>
       <c r="U124" s="3"/>
@@ -3356,7 +2425,7 @@
       <c r="AE124" s="2"/>
       <c r="AF124" s="2"/>
     </row>
-    <row r="125" ht="14.25" customHeight="1" spans="2:32">
+    <row r="125" ht="14.25" customHeight="1">
       <c r="B125" s="2"/>
       <c r="T125" s="2"/>
       <c r="U125" s="3"/>
@@ -3367,7 +2436,7 @@
       <c r="AE125" s="2"/>
       <c r="AF125" s="2"/>
     </row>
-    <row r="126" ht="14.25" customHeight="1" spans="2:32">
+    <row r="126" ht="14.25" customHeight="1">
       <c r="B126" s="2"/>
       <c r="T126" s="2"/>
       <c r="U126" s="3"/>
@@ -3378,7 +2447,7 @@
       <c r="AE126" s="2"/>
       <c r="AF126" s="2"/>
     </row>
-    <row r="127" ht="14.25" customHeight="1" spans="2:32">
+    <row r="127" ht="14.25" customHeight="1">
       <c r="B127" s="2"/>
       <c r="T127" s="2"/>
       <c r="U127" s="3"/>
@@ -3389,7 +2458,7 @@
       <c r="AE127" s="2"/>
       <c r="AF127" s="2"/>
     </row>
-    <row r="128" ht="14.25" customHeight="1" spans="2:32">
+    <row r="128" ht="14.25" customHeight="1">
       <c r="B128" s="2"/>
       <c r="T128" s="2"/>
       <c r="U128" s="3"/>
@@ -3400,7 +2469,7 @@
       <c r="AE128" s="2"/>
       <c r="AF128" s="2"/>
     </row>
-    <row r="129" ht="14.25" customHeight="1" spans="2:32">
+    <row r="129" ht="14.25" customHeight="1">
       <c r="B129" s="2"/>
       <c r="T129" s="2"/>
       <c r="U129" s="3"/>
@@ -3411,7 +2480,7 @@
       <c r="AE129" s="2"/>
       <c r="AF129" s="2"/>
     </row>
-    <row r="130" ht="14.25" customHeight="1" spans="2:32">
+    <row r="130" ht="14.25" customHeight="1">
       <c r="B130" s="2"/>
       <c r="T130" s="2"/>
       <c r="U130" s="3"/>
@@ -3422,7 +2491,7 @@
       <c r="AE130" s="2"/>
       <c r="AF130" s="2"/>
     </row>
-    <row r="131" ht="14.25" customHeight="1" spans="2:32">
+    <row r="131" ht="14.25" customHeight="1">
       <c r="B131" s="2"/>
       <c r="T131" s="2"/>
       <c r="U131" s="3"/>
@@ -3433,7 +2502,7 @@
       <c r="AE131" s="2"/>
       <c r="AF131" s="2"/>
     </row>
-    <row r="132" ht="14.25" customHeight="1" spans="2:32">
+    <row r="132" ht="14.25" customHeight="1">
       <c r="B132" s="2"/>
       <c r="T132" s="2"/>
       <c r="U132" s="3"/>
@@ -3444,7 +2513,7 @@
       <c r="AE132" s="2"/>
       <c r="AF132" s="2"/>
     </row>
-    <row r="133" ht="14.25" customHeight="1" spans="2:32">
+    <row r="133" ht="14.25" customHeight="1">
       <c r="B133" s="2"/>
       <c r="T133" s="2"/>
       <c r="U133" s="3"/>
@@ -3455,7 +2524,7 @@
       <c r="AE133" s="2"/>
       <c r="AF133" s="2"/>
     </row>
-    <row r="134" ht="14.25" customHeight="1" spans="2:32">
+    <row r="134" ht="14.25" customHeight="1">
       <c r="B134" s="2"/>
       <c r="T134" s="2"/>
       <c r="U134" s="3"/>
@@ -3466,7 +2535,7 @@
       <c r="AE134" s="2"/>
       <c r="AF134" s="2"/>
     </row>
-    <row r="135" ht="14.25" customHeight="1" spans="2:32">
+    <row r="135" ht="14.25" customHeight="1">
       <c r="B135" s="2"/>
       <c r="T135" s="2"/>
       <c r="U135" s="3"/>
@@ -3477,7 +2546,7 @@
       <c r="AE135" s="2"/>
       <c r="AF135" s="2"/>
     </row>
-    <row r="136" ht="14.25" customHeight="1" spans="2:32">
+    <row r="136" ht="14.25" customHeight="1">
       <c r="B136" s="2"/>
       <c r="T136" s="2"/>
       <c r="U136" s="3"/>
@@ -3488,7 +2557,7 @@
       <c r="AE136" s="2"/>
       <c r="AF136" s="2"/>
     </row>
-    <row r="137" ht="14.25" customHeight="1" spans="2:32">
+    <row r="137" ht="14.25" customHeight="1">
       <c r="B137" s="2"/>
       <c r="T137" s="2"/>
       <c r="U137" s="3"/>
@@ -3499,7 +2568,7 @@
       <c r="AE137" s="2"/>
       <c r="AF137" s="2"/>
     </row>
-    <row r="138" ht="14.25" customHeight="1" spans="2:32">
+    <row r="138" ht="14.25" customHeight="1">
       <c r="B138" s="2"/>
       <c r="T138" s="2"/>
       <c r="U138" s="3"/>
@@ -3510,7 +2579,7 @@
       <c r="AE138" s="2"/>
       <c r="AF138" s="2"/>
     </row>
-    <row r="139" ht="14.25" customHeight="1" spans="2:32">
+    <row r="139" ht="14.25" customHeight="1">
       <c r="B139" s="2"/>
       <c r="T139" s="2"/>
       <c r="U139" s="3"/>
@@ -3521,7 +2590,7 @@
       <c r="AE139" s="2"/>
       <c r="AF139" s="2"/>
     </row>
-    <row r="140" ht="14.25" customHeight="1" spans="2:32">
+    <row r="140" ht="14.25" customHeight="1">
       <c r="B140" s="2"/>
       <c r="T140" s="2"/>
       <c r="U140" s="3"/>
@@ -3532,7 +2601,7 @@
       <c r="AE140" s="2"/>
       <c r="AF140" s="2"/>
     </row>
-    <row r="141" ht="14.25" customHeight="1" spans="2:32">
+    <row r="141" ht="14.25" customHeight="1">
       <c r="B141" s="2"/>
       <c r="T141" s="2"/>
       <c r="U141" s="3"/>
@@ -3543,7 +2612,7 @@
       <c r="AE141" s="2"/>
       <c r="AF141" s="2"/>
     </row>
-    <row r="142" ht="14.25" customHeight="1" spans="2:32">
+    <row r="142" ht="14.25" customHeight="1">
       <c r="B142" s="2"/>
       <c r="T142" s="2"/>
       <c r="U142" s="3"/>
@@ -3554,7 +2623,7 @@
       <c r="AE142" s="2"/>
       <c r="AF142" s="2"/>
     </row>
-    <row r="143" ht="14.25" customHeight="1" spans="2:32">
+    <row r="143" ht="14.25" customHeight="1">
       <c r="B143" s="2"/>
       <c r="T143" s="2"/>
       <c r="U143" s="3"/>
@@ -3565,7 +2634,7 @@
       <c r="AE143" s="2"/>
       <c r="AF143" s="2"/>
     </row>
-    <row r="144" ht="14.25" customHeight="1" spans="2:32">
+    <row r="144" ht="14.25" customHeight="1">
       <c r="B144" s="2"/>
       <c r="T144" s="2"/>
       <c r="U144" s="3"/>
@@ -3576,7 +2645,7 @@
       <c r="AE144" s="2"/>
       <c r="AF144" s="2"/>
     </row>
-    <row r="145" ht="14.25" customHeight="1" spans="2:32">
+    <row r="145" ht="14.25" customHeight="1">
       <c r="B145" s="2"/>
       <c r="T145" s="2"/>
       <c r="U145" s="3"/>
@@ -3587,7 +2656,7 @@
       <c r="AE145" s="2"/>
       <c r="AF145" s="2"/>
     </row>
-    <row r="146" ht="14.25" customHeight="1" spans="2:32">
+    <row r="146" ht="14.25" customHeight="1">
       <c r="B146" s="2"/>
       <c r="T146" s="2"/>
       <c r="U146" s="3"/>
@@ -3598,7 +2667,7 @@
       <c r="AE146" s="2"/>
       <c r="AF146" s="2"/>
     </row>
-    <row r="147" ht="14.25" customHeight="1" spans="2:32">
+    <row r="147" ht="14.25" customHeight="1">
       <c r="B147" s="2"/>
       <c r="T147" s="2"/>
       <c r="U147" s="3"/>
@@ -3609,7 +2678,7 @@
       <c r="AE147" s="2"/>
       <c r="AF147" s="2"/>
     </row>
-    <row r="148" ht="14.25" customHeight="1" spans="2:32">
+    <row r="148" ht="14.25" customHeight="1">
       <c r="B148" s="2"/>
       <c r="T148" s="2"/>
       <c r="U148" s="3"/>
@@ -3620,7 +2689,7 @@
       <c r="AE148" s="2"/>
       <c r="AF148" s="2"/>
     </row>
-    <row r="149" ht="14.25" customHeight="1" spans="2:32">
+    <row r="149" ht="14.25" customHeight="1">
       <c r="B149" s="2"/>
       <c r="T149" s="2"/>
       <c r="U149" s="3"/>
@@ -3631,7 +2700,7 @@
       <c r="AE149" s="2"/>
       <c r="AF149" s="2"/>
     </row>
-    <row r="150" ht="14.25" customHeight="1" spans="2:32">
+    <row r="150" ht="14.25" customHeight="1">
       <c r="B150" s="2"/>
       <c r="T150" s="2"/>
       <c r="U150" s="3"/>
@@ -3642,7 +2711,7 @@
       <c r="AE150" s="2"/>
       <c r="AF150" s="2"/>
     </row>
-    <row r="151" ht="14.25" customHeight="1" spans="2:32">
+    <row r="151" ht="14.25" customHeight="1">
       <c r="B151" s="2"/>
       <c r="T151" s="2"/>
       <c r="U151" s="3"/>
@@ -3653,7 +2722,7 @@
       <c r="AE151" s="2"/>
       <c r="AF151" s="2"/>
     </row>
-    <row r="152" ht="14.25" customHeight="1" spans="2:32">
+    <row r="152" ht="14.25" customHeight="1">
       <c r="B152" s="2"/>
       <c r="T152" s="2"/>
       <c r="U152" s="3"/>
@@ -3664,7 +2733,7 @@
       <c r="AE152" s="2"/>
       <c r="AF152" s="2"/>
     </row>
-    <row r="153" ht="14.25" customHeight="1" spans="2:32">
+    <row r="153" ht="14.25" customHeight="1">
       <c r="B153" s="2"/>
       <c r="T153" s="2"/>
       <c r="U153" s="3"/>
@@ -3675,7 +2744,7 @@
       <c r="AE153" s="2"/>
       <c r="AF153" s="2"/>
     </row>
-    <row r="154" ht="14.25" customHeight="1" spans="2:32">
+    <row r="154" ht="14.25" customHeight="1">
       <c r="B154" s="2"/>
       <c r="T154" s="2"/>
       <c r="U154" s="3"/>
@@ -3686,7 +2755,7 @@
       <c r="AE154" s="2"/>
       <c r="AF154" s="2"/>
     </row>
-    <row r="155" ht="14.25" customHeight="1" spans="2:32">
+    <row r="155" ht="14.25" customHeight="1">
       <c r="B155" s="2"/>
       <c r="T155" s="2"/>
       <c r="U155" s="3"/>
@@ -3697,7 +2766,7 @@
       <c r="AE155" s="2"/>
       <c r="AF155" s="2"/>
     </row>
-    <row r="156" ht="14.25" customHeight="1" spans="2:32">
+    <row r="156" ht="14.25" customHeight="1">
       <c r="B156" s="2"/>
       <c r="T156" s="2"/>
       <c r="U156" s="3"/>
@@ -3708,7 +2777,7 @@
       <c r="AE156" s="2"/>
       <c r="AF156" s="2"/>
     </row>
-    <row r="157" ht="14.25" customHeight="1" spans="2:32">
+    <row r="157" ht="14.25" customHeight="1">
       <c r="B157" s="2"/>
       <c r="T157" s="2"/>
       <c r="U157" s="3"/>
@@ -3719,7 +2788,7 @@
       <c r="AE157" s="2"/>
       <c r="AF157" s="2"/>
     </row>
-    <row r="158" ht="14.25" customHeight="1" spans="2:32">
+    <row r="158" ht="14.25" customHeight="1">
       <c r="B158" s="2"/>
       <c r="T158" s="2"/>
       <c r="U158" s="3"/>
@@ -3730,7 +2799,7 @@
       <c r="AE158" s="2"/>
       <c r="AF158" s="2"/>
     </row>
-    <row r="159" ht="14.25" customHeight="1" spans="2:32">
+    <row r="159" ht="14.25" customHeight="1">
       <c r="B159" s="2"/>
       <c r="T159" s="2"/>
       <c r="U159" s="3"/>
@@ -3741,7 +2810,7 @@
       <c r="AE159" s="2"/>
       <c r="AF159" s="2"/>
     </row>
-    <row r="160" ht="14.25" customHeight="1" spans="2:32">
+    <row r="160" ht="14.25" customHeight="1">
       <c r="B160" s="2"/>
       <c r="T160" s="2"/>
       <c r="U160" s="3"/>
@@ -3752,7 +2821,7 @@
       <c r="AE160" s="2"/>
       <c r="AF160" s="2"/>
     </row>
-    <row r="161" ht="14.25" customHeight="1" spans="2:32">
+    <row r="161" ht="14.25" customHeight="1">
       <c r="B161" s="2"/>
       <c r="T161" s="2"/>
       <c r="U161" s="3"/>
@@ -3763,7 +2832,7 @@
       <c r="AE161" s="2"/>
       <c r="AF161" s="2"/>
     </row>
-    <row r="162" ht="14.25" customHeight="1" spans="2:32">
+    <row r="162" ht="14.25" customHeight="1">
       <c r="B162" s="2"/>
       <c r="T162" s="2"/>
       <c r="U162" s="3"/>
@@ -3774,7 +2843,7 @@
       <c r="AE162" s="2"/>
       <c r="AF162" s="2"/>
     </row>
-    <row r="163" ht="14.25" customHeight="1" spans="2:32">
+    <row r="163" ht="14.25" customHeight="1">
       <c r="B163" s="2"/>
       <c r="T163" s="2"/>
       <c r="U163" s="3"/>
@@ -3785,7 +2854,7 @@
       <c r="AE163" s="2"/>
       <c r="AF163" s="2"/>
     </row>
-    <row r="164" ht="14.25" customHeight="1" spans="2:32">
+    <row r="164" ht="14.25" customHeight="1">
       <c r="B164" s="2"/>
       <c r="T164" s="2"/>
       <c r="U164" s="3"/>
@@ -3796,7 +2865,7 @@
       <c r="AE164" s="2"/>
       <c r="AF164" s="2"/>
     </row>
-    <row r="165" ht="14.25" customHeight="1" spans="2:32">
+    <row r="165" ht="14.25" customHeight="1">
       <c r="B165" s="2"/>
       <c r="T165" s="2"/>
       <c r="U165" s="3"/>
@@ -3807,7 +2876,7 @@
       <c r="AE165" s="2"/>
       <c r="AF165" s="2"/>
     </row>
-    <row r="166" ht="14.25" customHeight="1" spans="2:32">
+    <row r="166" ht="14.25" customHeight="1">
       <c r="B166" s="2"/>
       <c r="T166" s="2"/>
       <c r="U166" s="3"/>
@@ -3818,7 +2887,7 @@
       <c r="AE166" s="2"/>
       <c r="AF166" s="2"/>
     </row>
-    <row r="167" ht="14.25" customHeight="1" spans="2:32">
+    <row r="167" ht="14.25" customHeight="1">
       <c r="B167" s="2"/>
       <c r="T167" s="2"/>
       <c r="U167" s="3"/>
@@ -3829,7 +2898,7 @@
       <c r="AE167" s="2"/>
       <c r="AF167" s="2"/>
     </row>
-    <row r="168" ht="14.25" customHeight="1" spans="2:32">
+    <row r="168" ht="14.25" customHeight="1">
       <c r="B168" s="2"/>
       <c r="T168" s="2"/>
       <c r="U168" s="3"/>
@@ -3840,7 +2909,7 @@
       <c r="AE168" s="2"/>
       <c r="AF168" s="2"/>
     </row>
-    <row r="169" ht="14.25" customHeight="1" spans="2:32">
+    <row r="169" ht="14.25" customHeight="1">
       <c r="B169" s="2"/>
       <c r="T169" s="2"/>
       <c r="U169" s="3"/>
@@ -3851,7 +2920,7 @@
       <c r="AE169" s="2"/>
       <c r="AF169" s="2"/>
     </row>
-    <row r="170" ht="14.25" customHeight="1" spans="2:32">
+    <row r="170" ht="14.25" customHeight="1">
       <c r="B170" s="2"/>
       <c r="T170" s="2"/>
       <c r="U170" s="3"/>
@@ -3862,7 +2931,7 @@
       <c r="AE170" s="2"/>
       <c r="AF170" s="2"/>
     </row>
-    <row r="171" ht="14.25" customHeight="1" spans="2:32">
+    <row r="171" ht="14.25" customHeight="1">
       <c r="B171" s="2"/>
       <c r="T171" s="2"/>
       <c r="U171" s="3"/>
@@ -3873,7 +2942,7 @@
       <c r="AE171" s="2"/>
       <c r="AF171" s="2"/>
     </row>
-    <row r="172" ht="14.25" customHeight="1" spans="2:32">
+    <row r="172" ht="14.25" customHeight="1">
       <c r="B172" s="2"/>
       <c r="T172" s="2"/>
       <c r="U172" s="3"/>
@@ -3884,7 +2953,7 @@
       <c r="AE172" s="2"/>
       <c r="AF172" s="2"/>
     </row>
-    <row r="173" ht="14.25" customHeight="1" spans="2:32">
+    <row r="173" ht="14.25" customHeight="1">
       <c r="B173" s="2"/>
       <c r="T173" s="2"/>
       <c r="U173" s="3"/>
@@ -3895,7 +2964,7 @@
       <c r="AE173" s="2"/>
       <c r="AF173" s="2"/>
     </row>
-    <row r="174" ht="14.25" customHeight="1" spans="2:32">
+    <row r="174" ht="14.25" customHeight="1">
       <c r="B174" s="2"/>
       <c r="T174" s="2"/>
       <c r="U174" s="3"/>
@@ -3906,7 +2975,7 @@
       <c r="AE174" s="2"/>
       <c r="AF174" s="2"/>
     </row>
-    <row r="175" ht="14.25" customHeight="1" spans="2:32">
+    <row r="175" ht="14.25" customHeight="1">
       <c r="B175" s="2"/>
       <c r="T175" s="2"/>
       <c r="U175" s="3"/>
@@ -3917,7 +2986,7 @@
       <c r="AE175" s="2"/>
       <c r="AF175" s="2"/>
     </row>
-    <row r="176" ht="14.25" customHeight="1" spans="2:32">
+    <row r="176" ht="14.25" customHeight="1">
       <c r="B176" s="2"/>
       <c r="T176" s="2"/>
       <c r="U176" s="3"/>
@@ -3928,7 +2997,7 @@
       <c r="AE176" s="2"/>
       <c r="AF176" s="2"/>
     </row>
-    <row r="177" ht="14.25" customHeight="1" spans="2:32">
+    <row r="177" ht="14.25" customHeight="1">
       <c r="B177" s="2"/>
       <c r="T177" s="2"/>
       <c r="U177" s="3"/>
@@ -3939,7 +3008,7 @@
       <c r="AE177" s="2"/>
       <c r="AF177" s="2"/>
     </row>
-    <row r="178" ht="14.25" customHeight="1" spans="2:32">
+    <row r="178" ht="14.25" customHeight="1">
       <c r="B178" s="2"/>
       <c r="T178" s="2"/>
       <c r="U178" s="3"/>
@@ -3950,7 +3019,7 @@
       <c r="AE178" s="2"/>
       <c r="AF178" s="2"/>
     </row>
-    <row r="179" ht="14.25" customHeight="1" spans="2:32">
+    <row r="179" ht="14.25" customHeight="1">
       <c r="B179" s="2"/>
       <c r="T179" s="2"/>
       <c r="U179" s="3"/>
@@ -3961,7 +3030,7 @@
       <c r="AE179" s="2"/>
       <c r="AF179" s="2"/>
     </row>
-    <row r="180" ht="14.25" customHeight="1" spans="2:32">
+    <row r="180" ht="14.25" customHeight="1">
       <c r="B180" s="2"/>
       <c r="T180" s="2"/>
       <c r="U180" s="3"/>
@@ -3972,7 +3041,7 @@
       <c r="AE180" s="2"/>
       <c r="AF180" s="2"/>
     </row>
-    <row r="181" ht="14.25" customHeight="1" spans="2:32">
+    <row r="181" ht="14.25" customHeight="1">
       <c r="B181" s="2"/>
       <c r="T181" s="2"/>
       <c r="U181" s="3"/>
@@ -3983,7 +3052,7 @@
       <c r="AE181" s="2"/>
       <c r="AF181" s="2"/>
     </row>
-    <row r="182" ht="14.25" customHeight="1" spans="2:32">
+    <row r="182" ht="14.25" customHeight="1">
       <c r="B182" s="2"/>
       <c r="T182" s="2"/>
       <c r="U182" s="3"/>
@@ -3994,7 +3063,7 @@
       <c r="AE182" s="2"/>
       <c r="AF182" s="2"/>
     </row>
-    <row r="183" ht="14.25" customHeight="1" spans="2:32">
+    <row r="183" ht="14.25" customHeight="1">
       <c r="B183" s="2"/>
       <c r="T183" s="2"/>
       <c r="U183" s="3"/>
@@ -4005,7 +3074,7 @@
       <c r="AE183" s="2"/>
       <c r="AF183" s="2"/>
     </row>
-    <row r="184" ht="14.25" customHeight="1" spans="2:32">
+    <row r="184" ht="14.25" customHeight="1">
       <c r="B184" s="2"/>
       <c r="T184" s="2"/>
       <c r="U184" s="3"/>
@@ -4016,7 +3085,7 @@
       <c r="AE184" s="2"/>
       <c r="AF184" s="2"/>
     </row>
-    <row r="185" ht="14.25" customHeight="1" spans="2:32">
+    <row r="185" ht="14.25" customHeight="1">
       <c r="B185" s="2"/>
       <c r="T185" s="2"/>
       <c r="U185" s="3"/>
@@ -4027,7 +3096,7 @@
       <c r="AE185" s="2"/>
       <c r="AF185" s="2"/>
     </row>
-    <row r="186" ht="14.25" customHeight="1" spans="2:32">
+    <row r="186" ht="14.25" customHeight="1">
       <c r="B186" s="2"/>
       <c r="T186" s="2"/>
       <c r="U186" s="3"/>
@@ -4038,7 +3107,7 @@
       <c r="AE186" s="2"/>
       <c r="AF186" s="2"/>
     </row>
-    <row r="187" ht="14.25" customHeight="1" spans="2:32">
+    <row r="187" ht="14.25" customHeight="1">
       <c r="B187" s="2"/>
       <c r="T187" s="2"/>
       <c r="U187" s="3"/>
@@ -4049,7 +3118,7 @@
       <c r="AE187" s="2"/>
       <c r="AF187" s="2"/>
     </row>
-    <row r="188" ht="14.25" customHeight="1" spans="2:32">
+    <row r="188" ht="14.25" customHeight="1">
       <c r="B188" s="2"/>
       <c r="T188" s="2"/>
       <c r="U188" s="3"/>
@@ -4060,7 +3129,7 @@
       <c r="AE188" s="2"/>
       <c r="AF188" s="2"/>
     </row>
-    <row r="189" ht="14.25" customHeight="1" spans="2:32">
+    <row r="189" ht="14.25" customHeight="1">
       <c r="B189" s="2"/>
       <c r="T189" s="2"/>
       <c r="U189" s="3"/>
@@ -4071,7 +3140,7 @@
       <c r="AE189" s="2"/>
       <c r="AF189" s="2"/>
     </row>
-    <row r="190" ht="14.25" customHeight="1" spans="2:32">
+    <row r="190" ht="14.25" customHeight="1">
       <c r="B190" s="2"/>
       <c r="T190" s="2"/>
       <c r="U190" s="3"/>
@@ -4082,7 +3151,7 @@
       <c r="AE190" s="2"/>
       <c r="AF190" s="2"/>
     </row>
-    <row r="191" ht="14.25" customHeight="1" spans="2:32">
+    <row r="191" ht="14.25" customHeight="1">
       <c r="B191" s="2"/>
       <c r="T191" s="2"/>
       <c r="U191" s="3"/>
@@ -4093,7 +3162,7 @@
       <c r="AE191" s="2"/>
       <c r="AF191" s="2"/>
     </row>
-    <row r="192" ht="14.25" customHeight="1" spans="2:32">
+    <row r="192" ht="14.25" customHeight="1">
       <c r="B192" s="2"/>
       <c r="T192" s="2"/>
       <c r="U192" s="3"/>
@@ -4104,7 +3173,7 @@
       <c r="AE192" s="2"/>
       <c r="AF192" s="2"/>
     </row>
-    <row r="193" ht="14.25" customHeight="1" spans="2:32">
+    <row r="193" ht="14.25" customHeight="1">
       <c r="B193" s="2"/>
       <c r="T193" s="2"/>
       <c r="U193" s="3"/>
@@ -4115,7 +3184,7 @@
       <c r="AE193" s="2"/>
       <c r="AF193" s="2"/>
     </row>
-    <row r="194" ht="14.25" customHeight="1" spans="2:32">
+    <row r="194" ht="14.25" customHeight="1">
       <c r="B194" s="2"/>
       <c r="T194" s="2"/>
       <c r="U194" s="3"/>
@@ -4126,7 +3195,7 @@
       <c r="AE194" s="2"/>
       <c r="AF194" s="2"/>
     </row>
-    <row r="195" ht="14.25" customHeight="1" spans="2:32">
+    <row r="195" ht="14.25" customHeight="1">
       <c r="B195" s="2"/>
       <c r="T195" s="2"/>
       <c r="U195" s="3"/>
@@ -4137,7 +3206,7 @@
       <c r="AE195" s="2"/>
       <c r="AF195" s="2"/>
     </row>
-    <row r="196" ht="14.25" customHeight="1" spans="2:32">
+    <row r="196" ht="14.25" customHeight="1">
       <c r="B196" s="2"/>
       <c r="T196" s="2"/>
       <c r="U196" s="3"/>
@@ -4148,7 +3217,7 @@
       <c r="AE196" s="2"/>
       <c r="AF196" s="2"/>
     </row>
-    <row r="197" ht="14.25" customHeight="1" spans="2:32">
+    <row r="197" ht="14.25" customHeight="1">
       <c r="B197" s="2"/>
       <c r="T197" s="2"/>
       <c r="U197" s="3"/>
@@ -4159,7 +3228,7 @@
       <c r="AE197" s="2"/>
       <c r="AF197" s="2"/>
     </row>
-    <row r="198" ht="14.25" customHeight="1" spans="2:32">
+    <row r="198" ht="14.25" customHeight="1">
       <c r="B198" s="2"/>
       <c r="T198" s="2"/>
       <c r="U198" s="3"/>
@@ -4170,7 +3239,7 @@
       <c r="AE198" s="2"/>
       <c r="AF198" s="2"/>
     </row>
-    <row r="199" ht="14.25" customHeight="1" spans="2:32">
+    <row r="199" ht="14.25" customHeight="1">
       <c r="B199" s="2"/>
       <c r="T199" s="2"/>
       <c r="U199" s="3"/>
@@ -4181,7 +3250,7 @@
       <c r="AE199" s="2"/>
       <c r="AF199" s="2"/>
     </row>
-    <row r="200" ht="14.25" customHeight="1" spans="2:32">
+    <row r="200" ht="14.25" customHeight="1">
       <c r="B200" s="2"/>
       <c r="T200" s="2"/>
       <c r="U200" s="3"/>
@@ -4192,7 +3261,7 @@
       <c r="AE200" s="2"/>
       <c r="AF200" s="2"/>
     </row>
-    <row r="201" ht="14.25" customHeight="1" spans="2:32">
+    <row r="201" ht="14.25" customHeight="1">
       <c r="B201" s="2"/>
       <c r="T201" s="2"/>
       <c r="U201" s="3"/>
@@ -4203,7 +3272,7 @@
       <c r="AE201" s="2"/>
       <c r="AF201" s="2"/>
     </row>
-    <row r="202" ht="14.25" customHeight="1" spans="2:32">
+    <row r="202" ht="14.25" customHeight="1">
       <c r="B202" s="2"/>
       <c r="T202" s="2"/>
       <c r="U202" s="3"/>
@@ -4214,7 +3283,7 @@
       <c r="AE202" s="2"/>
       <c r="AF202" s="2"/>
     </row>
-    <row r="203" ht="14.25" customHeight="1" spans="2:32">
+    <row r="203" ht="14.25" customHeight="1">
       <c r="B203" s="2"/>
       <c r="T203" s="2"/>
       <c r="U203" s="3"/>
@@ -4225,7 +3294,7 @@
       <c r="AE203" s="2"/>
       <c r="AF203" s="2"/>
     </row>
-    <row r="204" ht="14.25" customHeight="1" spans="2:32">
+    <row r="204" ht="14.25" customHeight="1">
       <c r="B204" s="2"/>
       <c r="T204" s="2"/>
       <c r="U204" s="3"/>
@@ -4236,7 +3305,7 @@
       <c r="AE204" s="2"/>
       <c r="AF204" s="2"/>
     </row>
-    <row r="205" ht="14.25" customHeight="1" spans="2:32">
+    <row r="205" ht="14.25" customHeight="1">
       <c r="B205" s="2"/>
       <c r="T205" s="2"/>
       <c r="U205" s="3"/>
@@ -4247,7 +3316,7 @@
       <c r="AE205" s="2"/>
       <c r="AF205" s="2"/>
     </row>
-    <row r="206" ht="14.25" customHeight="1" spans="2:32">
+    <row r="206" ht="14.25" customHeight="1">
       <c r="B206" s="2"/>
       <c r="T206" s="2"/>
       <c r="U206" s="3"/>
@@ -4258,7 +3327,7 @@
       <c r="AE206" s="2"/>
       <c r="AF206" s="2"/>
     </row>
-    <row r="207" ht="14.25" customHeight="1" spans="2:32">
+    <row r="207" ht="14.25" customHeight="1">
       <c r="B207" s="2"/>
       <c r="T207" s="2"/>
       <c r="U207" s="3"/>
@@ -4269,7 +3338,7 @@
       <c r="AE207" s="2"/>
       <c r="AF207" s="2"/>
     </row>
-    <row r="208" ht="14.25" customHeight="1" spans="2:32">
+    <row r="208" ht="14.25" customHeight="1">
       <c r="B208" s="2"/>
       <c r="T208" s="2"/>
       <c r="U208" s="3"/>
@@ -4280,7 +3349,7 @@
       <c r="AE208" s="2"/>
       <c r="AF208" s="2"/>
     </row>
-    <row r="209" ht="14.25" customHeight="1" spans="2:32">
+    <row r="209" ht="14.25" customHeight="1">
       <c r="B209" s="2"/>
       <c r="T209" s="2"/>
       <c r="U209" s="3"/>
@@ -4291,7 +3360,7 @@
       <c r="AE209" s="2"/>
       <c r="AF209" s="2"/>
     </row>
-    <row r="210" ht="14.25" customHeight="1" spans="2:32">
+    <row r="210" ht="14.25" customHeight="1">
       <c r="B210" s="2"/>
       <c r="T210" s="2"/>
       <c r="U210" s="3"/>
@@ -4302,7 +3371,7 @@
       <c r="AE210" s="2"/>
       <c r="AF210" s="2"/>
     </row>
-    <row r="211" ht="14.25" customHeight="1" spans="2:32">
+    <row r="211" ht="14.25" customHeight="1">
       <c r="B211" s="2"/>
       <c r="T211" s="2"/>
       <c r="U211" s="3"/>
@@ -4313,7 +3382,7 @@
       <c r="AE211" s="2"/>
       <c r="AF211" s="2"/>
     </row>
-    <row r="212" ht="14.25" customHeight="1" spans="2:32">
+    <row r="212" ht="14.25" customHeight="1">
       <c r="B212" s="2"/>
       <c r="T212" s="2"/>
       <c r="U212" s="3"/>
@@ -4324,7 +3393,7 @@
       <c r="AE212" s="2"/>
       <c r="AF212" s="2"/>
     </row>
-    <row r="213" ht="14.25" customHeight="1" spans="2:32">
+    <row r="213" ht="14.25" customHeight="1">
       <c r="B213" s="2"/>
       <c r="T213" s="2"/>
       <c r="U213" s="3"/>
@@ -4335,7 +3404,7 @@
       <c r="AE213" s="2"/>
       <c r="AF213" s="2"/>
     </row>
-    <row r="214" ht="14.25" customHeight="1" spans="2:32">
+    <row r="214" ht="14.25" customHeight="1">
       <c r="B214" s="2"/>
       <c r="T214" s="2"/>
       <c r="U214" s="3"/>
@@ -4346,7 +3415,7 @@
       <c r="AE214" s="2"/>
       <c r="AF214" s="2"/>
     </row>
-    <row r="215" ht="14.25" customHeight="1" spans="2:32">
+    <row r="215" ht="14.25" customHeight="1">
       <c r="B215" s="2"/>
       <c r="T215" s="2"/>
       <c r="U215" s="3"/>
@@ -4357,7 +3426,7 @@
       <c r="AE215" s="2"/>
       <c r="AF215" s="2"/>
     </row>
-    <row r="216" ht="14.25" customHeight="1" spans="2:32">
+    <row r="216" ht="14.25" customHeight="1">
       <c r="B216" s="2"/>
       <c r="T216" s="2"/>
       <c r="U216" s="3"/>
@@ -4368,7 +3437,7 @@
       <c r="AE216" s="2"/>
       <c r="AF216" s="2"/>
     </row>
-    <row r="217" ht="14.25" customHeight="1" spans="2:32">
+    <row r="217" ht="14.25" customHeight="1">
       <c r="B217" s="2"/>
       <c r="T217" s="2"/>
       <c r="U217" s="3"/>
@@ -4379,7 +3448,7 @@
       <c r="AE217" s="2"/>
       <c r="AF217" s="2"/>
     </row>
-    <row r="218" ht="14.25" customHeight="1" spans="2:32">
+    <row r="218" ht="14.25" customHeight="1">
       <c r="B218" s="2"/>
       <c r="T218" s="2"/>
       <c r="U218" s="3"/>
@@ -4390,7 +3459,7 @@
       <c r="AE218" s="2"/>
       <c r="AF218" s="2"/>
     </row>
-    <row r="219" ht="14.25" customHeight="1" spans="2:32">
+    <row r="219" ht="14.25" customHeight="1">
       <c r="B219" s="2"/>
       <c r="T219" s="2"/>
       <c r="U219" s="3"/>
@@ -4401,7 +3470,7 @@
       <c r="AE219" s="2"/>
       <c r="AF219" s="2"/>
     </row>
-    <row r="220" ht="14.25" customHeight="1" spans="2:32">
+    <row r="220" ht="14.25" customHeight="1">
       <c r="B220" s="2"/>
       <c r="T220" s="2"/>
       <c r="U220" s="3"/>
@@ -5193,9 +4262,9 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Templates/bulkImport/config/construct_RSDL_config_sslr.xlsx
+++ b/Templates/bulkImport/config/construct_RSDL_config_sslr.xlsx
@@ -1,13 +1,86 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9024"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="construct_RSDL_config_sarawak" sheetId="1" r:id="rId4"/>
+    <sheet name="construct_RSDL_config_sarawak" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="144525"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>USER</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AE5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -280,65 +353,923 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="24">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -528,53 +1459,53 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AQ1000"/>
+  <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.29"/>
-    <col customWidth="1" min="2" max="2" width="11.14"/>
-    <col customWidth="1" min="3" max="3" width="23.57"/>
-    <col customWidth="1" min="4" max="4" width="14.57"/>
-    <col customWidth="1" min="5" max="5" width="14.0"/>
-    <col customWidth="1" min="6" max="6" width="15.57"/>
-    <col customWidth="1" min="7" max="7" width="12.86"/>
-    <col customWidth="1" min="8" max="8" width="18.29"/>
-    <col customWidth="1" min="9" max="9" width="23.43"/>
-    <col customWidth="1" min="10" max="10" width="21.71"/>
-    <col customWidth="1" min="11" max="11" width="27.71"/>
-    <col customWidth="1" min="12" max="12" width="32.43"/>
-    <col customWidth="1" min="13" max="13" width="30.29"/>
-    <col customWidth="1" min="14" max="14" width="16.14"/>
-    <col customWidth="1" min="15" max="16" width="17.86"/>
-    <col customWidth="1" min="17" max="17" width="17.57"/>
-    <col customWidth="1" min="18" max="18" width="14.29"/>
-    <col customWidth="1" min="19" max="19" width="22.86"/>
-    <col customWidth="1" min="20" max="20" width="16.14"/>
-    <col customWidth="1" min="21" max="21" width="21.86"/>
-    <col customWidth="1" min="22" max="22" width="18.14"/>
-    <col customWidth="1" min="23" max="23" width="20.43"/>
-    <col customWidth="1" min="24" max="24" width="8.86"/>
-    <col customWidth="1" min="25" max="25" width="17.29"/>
-    <col customWidth="1" min="26" max="26" width="13.14"/>
-    <col customWidth="1" min="27" max="27" width="21.71"/>
-    <col customWidth="1" min="28" max="28" width="23.29"/>
-    <col customWidth="1" min="29" max="29" width="24.71"/>
-    <col customWidth="1" min="30" max="30" width="21.14"/>
-    <col customWidth="1" min="31" max="32" width="21.0"/>
-    <col customWidth="1" min="33" max="33" width="21.57"/>
-    <col customWidth="1" min="34" max="34" width="24.57"/>
-    <col customWidth="1" min="35" max="35" width="21.86"/>
-    <col customWidth="1" min="36" max="43" width="24.86"/>
+    <col min="1" max="1" width="10.287037037037" customWidth="1"/>
+    <col min="2" max="2" width="11.1388888888889" customWidth="1"/>
+    <col min="3" max="3" width="23.5740740740741" customWidth="1"/>
+    <col min="4" max="4" width="14.5740740740741" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="15.5740740740741" customWidth="1"/>
+    <col min="7" max="7" width="12.8611111111111" customWidth="1"/>
+    <col min="8" max="8" width="18.287037037037" customWidth="1"/>
+    <col min="9" max="9" width="23.4259259259259" customWidth="1"/>
+    <col min="10" max="10" width="21.712962962963" customWidth="1"/>
+    <col min="11" max="11" width="27.712962962963" customWidth="1"/>
+    <col min="12" max="12" width="32.4259259259259" customWidth="1"/>
+    <col min="13" max="13" width="30.287037037037" customWidth="1"/>
+    <col min="14" max="14" width="16.1388888888889" customWidth="1"/>
+    <col min="15" max="16" width="17.8611111111111" customWidth="1"/>
+    <col min="17" max="17" width="17.5740740740741" customWidth="1"/>
+    <col min="18" max="18" width="14.287037037037" customWidth="1"/>
+    <col min="19" max="19" width="22.8611111111111" customWidth="1"/>
+    <col min="20" max="20" width="16.1388888888889" customWidth="1"/>
+    <col min="21" max="21" width="21.8611111111111" customWidth="1"/>
+    <col min="22" max="22" width="18.1388888888889" customWidth="1"/>
+    <col min="23" max="23" width="20.4259259259259" customWidth="1"/>
+    <col min="24" max="24" width="8.86111111111111" customWidth="1"/>
+    <col min="25" max="25" width="17.287037037037" customWidth="1"/>
+    <col min="26" max="26" width="13.1388888888889" customWidth="1"/>
+    <col min="27" max="27" width="21.712962962963" customWidth="1"/>
+    <col min="28" max="28" width="23.287037037037" customWidth="1"/>
+    <col min="29" max="29" width="24.712962962963" customWidth="1"/>
+    <col min="30" max="30" width="21.1388888888889" customWidth="1"/>
+    <col min="31" max="32" width="21" customWidth="1"/>
+    <col min="33" max="33" width="21.5740740740741" customWidth="1"/>
+    <col min="34" max="34" width="24.5740740740741" customWidth="1"/>
+    <col min="35" max="35" width="21.8611111111111" customWidth="1"/>
+    <col min="36" max="43" width="24.8611111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" ht="14.25" customHeight="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,7 +1527,7 @@
       <c r="AE1" s="2"/>
       <c r="AF1" s="2"/>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" ht="14.25" customHeight="1" spans="1:43">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -669,7 +1600,7 @@
       <c r="X2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Y2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="Z2" s="1" t="s">
@@ -703,7 +1634,7 @@
       <c r="AJ2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="5" t="s">
+      <c r="AK2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="AL2" s="1" t="s">
@@ -715,146 +1646,146 @@
       <c r="AN2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AO2" s="5" t="s">
+      <c r="AO2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="AP2" s="5"/>
+      <c r="AP2" s="4"/>
       <c r="AQ2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" ht="14.25" customHeight="1" spans="1:43">
       <c r="A3" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B3" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E3" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F3" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G3" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H3" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I3" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J3" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="K3" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="L3" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="M3" s="3">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="N3" s="3">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="O3" s="3">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="P3" s="3">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="Q3" s="3">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="R3" s="3">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="S3" s="3">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="T3" s="3">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="U3" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="V3" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="W3" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="X3" s="3">
-        <v>23.0</v>
-      </c>
-      <c r="Y3" s="4">
-        <v>24.0</v>
-      </c>
-      <c r="Z3" s="4">
-        <v>25.0</v>
-      </c>
-      <c r="AA3" s="4">
-        <v>26.0</v>
-      </c>
-      <c r="AB3" s="4">
-        <v>27.0</v>
-      </c>
-      <c r="AC3" s="4">
-        <v>28.0</v>
-      </c>
-      <c r="AD3" s="4">
-        <v>29.0</v>
-      </c>
-      <c r="AE3" s="4">
-        <v>30.0</v>
-      </c>
-      <c r="AF3" s="4">
-        <v>31.0</v>
-      </c>
-      <c r="AG3" s="4">
-        <v>32.0</v>
-      </c>
-      <c r="AH3" s="4">
-        <v>33.0</v>
-      </c>
-      <c r="AI3" s="4">
-        <v>34.0</v>
-      </c>
-      <c r="AJ3" s="4">
-        <v>35.0</v>
-      </c>
-      <c r="AK3" s="4">
-        <v>36.0</v>
-      </c>
-      <c r="AL3" s="4">
-        <v>37.0</v>
-      </c>
-      <c r="AM3" s="4">
-        <v>38.0</v>
-      </c>
-      <c r="AN3" s="4">
-        <v>39.0</v>
-      </c>
-      <c r="AO3" s="4">
-        <v>40.0</v>
-      </c>
-      <c r="AP3" s="4">
-        <v>41.0</v>
-      </c>
-      <c r="AQ3" s="4">
-        <v>42.0</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="5">
+        <v>24</v>
+      </c>
+      <c r="Z3" s="5">
+        <v>25</v>
+      </c>
+      <c r="AA3" s="5">
+        <v>26</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>27</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>28</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>29</v>
+      </c>
+      <c r="AE3" s="5">
+        <v>30</v>
+      </c>
+      <c r="AF3" s="5">
+        <v>31</v>
+      </c>
+      <c r="AG3" s="5">
+        <v>32</v>
+      </c>
+      <c r="AH3" s="5">
+        <v>33</v>
+      </c>
+      <c r="AI3" s="5">
+        <v>34</v>
+      </c>
+      <c r="AJ3" s="5">
+        <v>35</v>
+      </c>
+      <c r="AK3" s="5">
+        <v>36</v>
+      </c>
+      <c r="AL3" s="5">
+        <v>37</v>
+      </c>
+      <c r="AM3" s="5">
+        <v>38</v>
+      </c>
+      <c r="AN3" s="5">
+        <v>39</v>
+      </c>
+      <c r="AO3" s="5">
+        <v>40</v>
+      </c>
+      <c r="AP3" s="5">
+        <v>41</v>
+      </c>
+      <c r="AQ3" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1" spans="1:43">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -927,7 +1858,7 @@
       <c r="X4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Y4" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Z4" s="1" t="s">
@@ -963,7 +1894,7 @@
       <c r="AJ4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AK4" s="5" t="s">
+      <c r="AK4" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AL4" s="1" t="s">
@@ -975,24 +1906,24 @@
       <c r="AN4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AO4" s="5" t="s">
+      <c r="AO4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AP4" s="5" t="s">
+      <c r="AP4" s="4" t="s">
         <v>44</v>
       </c>
       <c r="AQ4" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" ht="14.25" customHeight="1" spans="1:43">
       <c r="A5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1058,7 +1989,7 @@
       <c r="X5" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="Y5" s="5" t="s">
         <v>70</v>
       </c>
       <c r="Z5" s="1" t="s">
@@ -1094,29 +2025,29 @@
       <c r="AJ5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AK5" s="4" t="s">
+      <c r="AK5" s="5" t="s">
         <v>81</v>
       </c>
       <c r="AL5" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="AM5" s="4" t="s">
+      <c r="AM5" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="AN5" s="4" t="s">
+      <c r="AN5" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AO5" s="4" t="s">
+      <c r="AO5" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="AP5" s="4" t="s">
+      <c r="AP5" s="5" t="s">
         <v>86</v>
       </c>
       <c r="AQ5" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" ht="14.25" customHeight="1" spans="2:32">
       <c r="B6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="3"/>
@@ -1127,7 +2058,7 @@
       <c r="AE6" s="2"/>
       <c r="AF6" s="2"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" ht="14.25" customHeight="1" spans="2:32">
       <c r="B7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="3"/>
@@ -1138,7 +2069,7 @@
       <c r="AE7" s="2"/>
       <c r="AF7" s="2"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" ht="14.25" customHeight="1" spans="2:32">
       <c r="B8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="3"/>
@@ -1149,7 +2080,7 @@
       <c r="AE8" s="2"/>
       <c r="AF8" s="2"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" ht="14.25" customHeight="1" spans="2:32">
       <c r="B9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="3"/>
@@ -1160,7 +2091,7 @@
       <c r="AE9" s="2"/>
       <c r="AF9" s="2"/>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" ht="14.25" customHeight="1" spans="2:32">
       <c r="B10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="3"/>
@@ -1171,7 +2102,7 @@
       <c r="AE10" s="2"/>
       <c r="AF10" s="2"/>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" ht="14.25" customHeight="1" spans="2:32">
       <c r="B11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="3"/>
@@ -1182,7 +2113,7 @@
       <c r="AE11" s="2"/>
       <c r="AF11" s="2"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" ht="14.25" customHeight="1" spans="2:32">
       <c r="B12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="3"/>
@@ -1193,7 +2124,7 @@
       <c r="AE12" s="2"/>
       <c r="AF12" s="2"/>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" ht="14.25" customHeight="1" spans="2:32">
       <c r="B13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="3"/>
@@ -1204,7 +2135,7 @@
       <c r="AE13" s="2"/>
       <c r="AF13" s="2"/>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" ht="14.25" customHeight="1" spans="2:32">
       <c r="B14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="3"/>
@@ -1215,7 +2146,7 @@
       <c r="AE14" s="2"/>
       <c r="AF14" s="2"/>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" ht="14.25" customHeight="1" spans="2:32">
       <c r="B15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="3"/>
@@ -1226,7 +2157,7 @@
       <c r="AE15" s="2"/>
       <c r="AF15" s="2"/>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" ht="14.25" customHeight="1" spans="2:32">
       <c r="B16" s="2"/>
       <c r="T16" s="2"/>
       <c r="U16" s="3"/>
@@ -1237,7 +2168,7 @@
       <c r="AE16" s="2"/>
       <c r="AF16" s="2"/>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" ht="14.25" customHeight="1" spans="2:32">
       <c r="B17" s="2"/>
       <c r="T17" s="2"/>
       <c r="U17" s="3"/>
@@ -1248,7 +2179,7 @@
       <c r="AE17" s="2"/>
       <c r="AF17" s="2"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" ht="14.25" customHeight="1" spans="2:32">
       <c r="B18" s="2"/>
       <c r="T18" s="2"/>
       <c r="U18" s="3"/>
@@ -1259,7 +2190,7 @@
       <c r="AE18" s="2"/>
       <c r="AF18" s="2"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" ht="14.25" customHeight="1" spans="2:32">
       <c r="B19" s="2"/>
       <c r="T19" s="2"/>
       <c r="U19" s="3"/>
@@ -1270,7 +2201,7 @@
       <c r="AE19" s="2"/>
       <c r="AF19" s="2"/>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" ht="14.25" customHeight="1" spans="2:32">
       <c r="B20" s="2"/>
       <c r="T20" s="2"/>
       <c r="U20" s="3"/>
@@ -1281,7 +2212,7 @@
       <c r="AE20" s="2"/>
       <c r="AF20" s="2"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" ht="14.25" customHeight="1" spans="2:32">
       <c r="B21" s="2"/>
       <c r="T21" s="2"/>
       <c r="U21" s="3"/>
@@ -1292,7 +2223,7 @@
       <c r="AE21" s="2"/>
       <c r="AF21" s="2"/>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22" ht="14.25" customHeight="1" spans="2:32">
       <c r="B22" s="2"/>
       <c r="T22" s="2"/>
       <c r="U22" s="3"/>
@@ -1303,7 +2234,7 @@
       <c r="AE22" s="2"/>
       <c r="AF22" s="2"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23" ht="14.25" customHeight="1" spans="2:32">
       <c r="B23" s="2"/>
       <c r="T23" s="2"/>
       <c r="U23" s="3"/>
@@ -1314,7 +2245,7 @@
       <c r="AE23" s="2"/>
       <c r="AF23" s="2"/>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24" ht="14.25" customHeight="1" spans="2:32">
       <c r="B24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="3"/>
@@ -1325,7 +2256,7 @@
       <c r="AE24" s="2"/>
       <c r="AF24" s="2"/>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" ht="14.25" customHeight="1" spans="2:32">
       <c r="B25" s="2"/>
       <c r="T25" s="2"/>
       <c r="U25" s="3"/>
@@ -1336,7 +2267,7 @@
       <c r="AE25" s="2"/>
       <c r="AF25" s="2"/>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
+    <row r="26" ht="14.25" customHeight="1" spans="2:32">
       <c r="B26" s="2"/>
       <c r="T26" s="2"/>
       <c r="U26" s="3"/>
@@ -1347,7 +2278,7 @@
       <c r="AE26" s="2"/>
       <c r="AF26" s="2"/>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
+    <row r="27" ht="14.25" customHeight="1" spans="2:32">
       <c r="B27" s="2"/>
       <c r="T27" s="2"/>
       <c r="U27" s="3"/>
@@ -1358,7 +2289,7 @@
       <c r="AE27" s="2"/>
       <c r="AF27" s="2"/>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" ht="14.25" customHeight="1" spans="2:32">
       <c r="B28" s="2"/>
       <c r="T28" s="2"/>
       <c r="U28" s="3"/>
@@ -1369,7 +2300,7 @@
       <c r="AE28" s="2"/>
       <c r="AF28" s="2"/>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" ht="14.25" customHeight="1" spans="2:32">
       <c r="B29" s="2"/>
       <c r="T29" s="2"/>
       <c r="U29" s="3"/>
@@ -1380,7 +2311,7 @@
       <c r="AE29" s="2"/>
       <c r="AF29" s="2"/>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" ht="14.25" customHeight="1" spans="2:32">
       <c r="B30" s="2"/>
       <c r="T30" s="2"/>
       <c r="U30" s="3"/>
@@ -1391,7 +2322,7 @@
       <c r="AE30" s="2"/>
       <c r="AF30" s="2"/>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" ht="14.25" customHeight="1" spans="2:32">
       <c r="B31" s="2"/>
       <c r="T31" s="2"/>
       <c r="U31" s="3"/>
@@ -1402,7 +2333,7 @@
       <c r="AE31" s="2"/>
       <c r="AF31" s="2"/>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" ht="14.25" customHeight="1" spans="2:32">
       <c r="B32" s="2"/>
       <c r="T32" s="2"/>
       <c r="U32" s="3"/>
@@ -1413,7 +2344,7 @@
       <c r="AE32" s="2"/>
       <c r="AF32" s="2"/>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" ht="14.25" customHeight="1" spans="2:32">
       <c r="B33" s="2"/>
       <c r="T33" s="2"/>
       <c r="U33" s="3"/>
@@ -1424,7 +2355,7 @@
       <c r="AE33" s="2"/>
       <c r="AF33" s="2"/>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" ht="14.25" customHeight="1" spans="2:32">
       <c r="B34" s="2"/>
       <c r="T34" s="2"/>
       <c r="U34" s="3"/>
@@ -1435,7 +2366,7 @@
       <c r="AE34" s="2"/>
       <c r="AF34" s="2"/>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" ht="14.25" customHeight="1" spans="2:32">
       <c r="B35" s="2"/>
       <c r="T35" s="2"/>
       <c r="U35" s="3"/>
@@ -1446,7 +2377,7 @@
       <c r="AE35" s="2"/>
       <c r="AF35" s="2"/>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
+    <row r="36" ht="14.25" customHeight="1" spans="2:32">
       <c r="B36" s="2"/>
       <c r="T36" s="2"/>
       <c r="U36" s="3"/>
@@ -1457,7 +2388,7 @@
       <c r="AE36" s="2"/>
       <c r="AF36" s="2"/>
     </row>
-    <row r="37" ht="14.25" customHeight="1">
+    <row r="37" ht="14.25" customHeight="1" spans="2:32">
       <c r="B37" s="2"/>
       <c r="T37" s="2"/>
       <c r="U37" s="3"/>
@@ -1468,7 +2399,7 @@
       <c r="AE37" s="2"/>
       <c r="AF37" s="2"/>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38" ht="14.25" customHeight="1" spans="2:32">
       <c r="B38" s="2"/>
       <c r="T38" s="2"/>
       <c r="U38" s="3"/>
@@ -1479,7 +2410,7 @@
       <c r="AE38" s="2"/>
       <c r="AF38" s="2"/>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
+    <row r="39" ht="14.25" customHeight="1" spans="2:32">
       <c r="B39" s="2"/>
       <c r="T39" s="2"/>
       <c r="U39" s="3"/>
@@ -1490,7 +2421,7 @@
       <c r="AE39" s="2"/>
       <c r="AF39" s="2"/>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
+    <row r="40" ht="14.25" customHeight="1" spans="2:32">
       <c r="B40" s="2"/>
       <c r="T40" s="2"/>
       <c r="U40" s="3"/>
@@ -1501,7 +2432,7 @@
       <c r="AE40" s="2"/>
       <c r="AF40" s="2"/>
     </row>
-    <row r="41" ht="14.25" customHeight="1">
+    <row r="41" ht="14.25" customHeight="1" spans="2:32">
       <c r="B41" s="2"/>
       <c r="T41" s="2"/>
       <c r="U41" s="3"/>
@@ -1512,7 +2443,7 @@
       <c r="AE41" s="2"/>
       <c r="AF41" s="2"/>
     </row>
-    <row r="42" ht="14.25" customHeight="1">
+    <row r="42" ht="14.25" customHeight="1" spans="2:32">
       <c r="B42" s="2"/>
       <c r="T42" s="2"/>
       <c r="U42" s="3"/>
@@ -1523,7 +2454,7 @@
       <c r="AE42" s="2"/>
       <c r="AF42" s="2"/>
     </row>
-    <row r="43" ht="14.25" customHeight="1">
+    <row r="43" ht="14.25" customHeight="1" spans="2:32">
       <c r="B43" s="2"/>
       <c r="T43" s="2"/>
       <c r="U43" s="3"/>
@@ -1534,7 +2465,7 @@
       <c r="AE43" s="2"/>
       <c r="AF43" s="2"/>
     </row>
-    <row r="44" ht="14.25" customHeight="1">
+    <row r="44" ht="14.25" customHeight="1" spans="2:32">
       <c r="B44" s="2"/>
       <c r="T44" s="2"/>
       <c r="U44" s="3"/>
@@ -1545,7 +2476,7 @@
       <c r="AE44" s="2"/>
       <c r="AF44" s="2"/>
     </row>
-    <row r="45" ht="14.25" customHeight="1">
+    <row r="45" ht="14.25" customHeight="1" spans="2:32">
       <c r="B45" s="2"/>
       <c r="T45" s="2"/>
       <c r="U45" s="3"/>
@@ -1556,7 +2487,7 @@
       <c r="AE45" s="2"/>
       <c r="AF45" s="2"/>
     </row>
-    <row r="46" ht="14.25" customHeight="1">
+    <row r="46" ht="14.25" customHeight="1" spans="2:32">
       <c r="B46" s="2"/>
       <c r="T46" s="2"/>
       <c r="U46" s="3"/>
@@ -1567,7 +2498,7 @@
       <c r="AE46" s="2"/>
       <c r="AF46" s="2"/>
     </row>
-    <row r="47" ht="14.25" customHeight="1">
+    <row r="47" ht="14.25" customHeight="1" spans="2:32">
       <c r="B47" s="2"/>
       <c r="T47" s="2"/>
       <c r="U47" s="3"/>
@@ -1578,7 +2509,7 @@
       <c r="AE47" s="2"/>
       <c r="AF47" s="2"/>
     </row>
-    <row r="48" ht="14.25" customHeight="1">
+    <row r="48" ht="14.25" customHeight="1" spans="2:32">
       <c r="B48" s="2"/>
       <c r="T48" s="2"/>
       <c r="U48" s="3"/>
@@ -1589,7 +2520,7 @@
       <c r="AE48" s="2"/>
       <c r="AF48" s="2"/>
     </row>
-    <row r="49" ht="14.25" customHeight="1">
+    <row r="49" ht="14.25" customHeight="1" spans="2:32">
       <c r="B49" s="2"/>
       <c r="T49" s="2"/>
       <c r="U49" s="3"/>
@@ -1600,7 +2531,7 @@
       <c r="AE49" s="2"/>
       <c r="AF49" s="2"/>
     </row>
-    <row r="50" ht="14.25" customHeight="1">
+    <row r="50" ht="14.25" customHeight="1" spans="2:32">
       <c r="B50" s="2"/>
       <c r="T50" s="2"/>
       <c r="U50" s="3"/>
@@ -1611,7 +2542,7 @@
       <c r="AE50" s="2"/>
       <c r="AF50" s="2"/>
     </row>
-    <row r="51" ht="14.25" customHeight="1">
+    <row r="51" ht="14.25" customHeight="1" spans="2:32">
       <c r="B51" s="2"/>
       <c r="T51" s="2"/>
       <c r="U51" s="3"/>
@@ -1622,7 +2553,7 @@
       <c r="AE51" s="2"/>
       <c r="AF51" s="2"/>
     </row>
-    <row r="52" ht="14.25" customHeight="1">
+    <row r="52" ht="14.25" customHeight="1" spans="2:32">
       <c r="B52" s="2"/>
       <c r="T52" s="2"/>
       <c r="U52" s="3"/>
@@ -1633,7 +2564,7 @@
       <c r="AE52" s="2"/>
       <c r="AF52" s="2"/>
     </row>
-    <row r="53" ht="14.25" customHeight="1">
+    <row r="53" ht="14.25" customHeight="1" spans="2:32">
       <c r="B53" s="2"/>
       <c r="T53" s="2"/>
       <c r="U53" s="3"/>
@@ -1644,7 +2575,7 @@
       <c r="AE53" s="2"/>
       <c r="AF53" s="2"/>
     </row>
-    <row r="54" ht="14.25" customHeight="1">
+    <row r="54" ht="14.25" customHeight="1" spans="2:32">
       <c r="B54" s="2"/>
       <c r="T54" s="2"/>
       <c r="U54" s="3"/>
@@ -1655,7 +2586,7 @@
       <c r="AE54" s="2"/>
       <c r="AF54" s="2"/>
     </row>
-    <row r="55" ht="14.25" customHeight="1">
+    <row r="55" ht="14.25" customHeight="1" spans="2:32">
       <c r="B55" s="2"/>
       <c r="T55" s="2"/>
       <c r="U55" s="3"/>
@@ -1666,7 +2597,7 @@
       <c r="AE55" s="2"/>
       <c r="AF55" s="2"/>
     </row>
-    <row r="56" ht="14.25" customHeight="1">
+    <row r="56" ht="14.25" customHeight="1" spans="2:32">
       <c r="B56" s="2"/>
       <c r="T56" s="2"/>
       <c r="U56" s="3"/>
@@ -1677,7 +2608,7 @@
       <c r="AE56" s="2"/>
       <c r="AF56" s="2"/>
     </row>
-    <row r="57" ht="14.25" customHeight="1">
+    <row r="57" ht="14.25" customHeight="1" spans="2:32">
       <c r="B57" s="2"/>
       <c r="T57" s="2"/>
       <c r="U57" s="3"/>
@@ -1688,7 +2619,7 @@
       <c r="AE57" s="2"/>
       <c r="AF57" s="2"/>
     </row>
-    <row r="58" ht="14.25" customHeight="1">
+    <row r="58" ht="14.25" customHeight="1" spans="2:32">
       <c r="B58" s="2"/>
       <c r="T58" s="2"/>
       <c r="U58" s="3"/>
@@ -1699,7 +2630,7 @@
       <c r="AE58" s="2"/>
       <c r="AF58" s="2"/>
     </row>
-    <row r="59" ht="14.25" customHeight="1">
+    <row r="59" ht="14.25" customHeight="1" spans="2:32">
       <c r="B59" s="2"/>
       <c r="T59" s="2"/>
       <c r="U59" s="3"/>
@@ -1710,7 +2641,7 @@
       <c r="AE59" s="2"/>
       <c r="AF59" s="2"/>
     </row>
-    <row r="60" ht="14.25" customHeight="1">
+    <row r="60" ht="14.25" customHeight="1" spans="2:32">
       <c r="B60" s="2"/>
       <c r="T60" s="2"/>
       <c r="U60" s="3"/>
@@ -1721,7 +2652,7 @@
       <c r="AE60" s="2"/>
       <c r="AF60" s="2"/>
     </row>
-    <row r="61" ht="14.25" customHeight="1">
+    <row r="61" ht="14.25" customHeight="1" spans="2:32">
       <c r="B61" s="2"/>
       <c r="T61" s="2"/>
       <c r="U61" s="3"/>
@@ -1732,7 +2663,7 @@
       <c r="AE61" s="2"/>
       <c r="AF61" s="2"/>
     </row>
-    <row r="62" ht="14.25" customHeight="1">
+    <row r="62" ht="14.25" customHeight="1" spans="2:32">
       <c r="B62" s="2"/>
       <c r="T62" s="2"/>
       <c r="U62" s="3"/>
@@ -1743,7 +2674,7 @@
       <c r="AE62" s="2"/>
       <c r="AF62" s="2"/>
     </row>
-    <row r="63" ht="14.25" customHeight="1">
+    <row r="63" ht="14.25" customHeight="1" spans="2:32">
       <c r="B63" s="2"/>
       <c r="T63" s="2"/>
       <c r="U63" s="3"/>
@@ -1754,7 +2685,7 @@
       <c r="AE63" s="2"/>
       <c r="AF63" s="2"/>
     </row>
-    <row r="64" ht="14.25" customHeight="1">
+    <row r="64" ht="14.25" customHeight="1" spans="2:32">
       <c r="B64" s="2"/>
       <c r="T64" s="2"/>
       <c r="U64" s="3"/>
@@ -1765,7 +2696,7 @@
       <c r="AE64" s="2"/>
       <c r="AF64" s="2"/>
     </row>
-    <row r="65" ht="14.25" customHeight="1">
+    <row r="65" ht="14.25" customHeight="1" spans="2:32">
       <c r="B65" s="2"/>
       <c r="T65" s="2"/>
       <c r="U65" s="3"/>
@@ -1776,7 +2707,7 @@
       <c r="AE65" s="2"/>
       <c r="AF65" s="2"/>
     </row>
-    <row r="66" ht="14.25" customHeight="1">
+    <row r="66" ht="14.25" customHeight="1" spans="2:32">
       <c r="B66" s="2"/>
       <c r="T66" s="2"/>
       <c r="U66" s="3"/>
@@ -1787,7 +2718,7 @@
       <c r="AE66" s="2"/>
       <c r="AF66" s="2"/>
     </row>
-    <row r="67" ht="14.25" customHeight="1">
+    <row r="67" ht="14.25" customHeight="1" spans="2:32">
       <c r="B67" s="2"/>
       <c r="T67" s="2"/>
       <c r="U67" s="3"/>
@@ -1798,7 +2729,7 @@
       <c r="AE67" s="2"/>
       <c r="AF67" s="2"/>
     </row>
-    <row r="68" ht="14.25" customHeight="1">
+    <row r="68" ht="14.25" customHeight="1" spans="2:32">
       <c r="B68" s="2"/>
       <c r="T68" s="2"/>
       <c r="U68" s="3"/>
@@ -1809,7 +2740,7 @@
       <c r="AE68" s="2"/>
       <c r="AF68" s="2"/>
     </row>
-    <row r="69" ht="14.25" customHeight="1">
+    <row r="69" ht="14.25" customHeight="1" spans="2:32">
       <c r="B69" s="2"/>
       <c r="T69" s="2"/>
       <c r="U69" s="3"/>
@@ -1820,7 +2751,7 @@
       <c r="AE69" s="2"/>
       <c r="AF69" s="2"/>
     </row>
-    <row r="70" ht="14.25" customHeight="1">
+    <row r="70" ht="14.25" customHeight="1" spans="2:32">
       <c r="B70" s="2"/>
       <c r="T70" s="2"/>
       <c r="U70" s="3"/>
@@ -1831,7 +2762,7 @@
       <c r="AE70" s="2"/>
       <c r="AF70" s="2"/>
     </row>
-    <row r="71" ht="14.25" customHeight="1">
+    <row r="71" ht="14.25" customHeight="1" spans="2:32">
       <c r="B71" s="2"/>
       <c r="T71" s="2"/>
       <c r="U71" s="3"/>
@@ -1842,7 +2773,7 @@
       <c r="AE71" s="2"/>
       <c r="AF71" s="2"/>
     </row>
-    <row r="72" ht="14.25" customHeight="1">
+    <row r="72" ht="14.25" customHeight="1" spans="2:32">
       <c r="B72" s="2"/>
       <c r="T72" s="2"/>
       <c r="U72" s="3"/>
@@ -1853,7 +2784,7 @@
       <c r="AE72" s="2"/>
       <c r="AF72" s="2"/>
     </row>
-    <row r="73" ht="14.25" customHeight="1">
+    <row r="73" ht="14.25" customHeight="1" spans="2:32">
       <c r="B73" s="2"/>
       <c r="T73" s="2"/>
       <c r="U73" s="3"/>
@@ -1864,7 +2795,7 @@
       <c r="AE73" s="2"/>
       <c r="AF73" s="2"/>
     </row>
-    <row r="74" ht="14.25" customHeight="1">
+    <row r="74" ht="14.25" customHeight="1" spans="2:32">
       <c r="B74" s="2"/>
       <c r="T74" s="2"/>
       <c r="U74" s="3"/>
@@ -1875,7 +2806,7 @@
       <c r="AE74" s="2"/>
       <c r="AF74" s="2"/>
     </row>
-    <row r="75" ht="14.25" customHeight="1">
+    <row r="75" ht="14.25" customHeight="1" spans="2:32">
       <c r="B75" s="2"/>
       <c r="T75" s="2"/>
       <c r="U75" s="3"/>
@@ -1886,7 +2817,7 @@
       <c r="AE75" s="2"/>
       <c r="AF75" s="2"/>
     </row>
-    <row r="76" ht="14.25" customHeight="1">
+    <row r="76" ht="14.25" customHeight="1" spans="2:32">
       <c r="B76" s="2"/>
       <c r="T76" s="2"/>
       <c r="U76" s="3"/>
@@ -1897,7 +2828,7 @@
       <c r="AE76" s="2"/>
       <c r="AF76" s="2"/>
     </row>
-    <row r="77" ht="14.25" customHeight="1">
+    <row r="77" ht="14.25" customHeight="1" spans="2:32">
       <c r="B77" s="2"/>
       <c r="T77" s="2"/>
       <c r="U77" s="3"/>
@@ -1908,7 +2839,7 @@
       <c r="AE77" s="2"/>
       <c r="AF77" s="2"/>
     </row>
-    <row r="78" ht="14.25" customHeight="1">
+    <row r="78" ht="14.25" customHeight="1" spans="2:32">
       <c r="B78" s="2"/>
       <c r="T78" s="2"/>
       <c r="U78" s="3"/>
@@ -1919,7 +2850,7 @@
       <c r="AE78" s="2"/>
       <c r="AF78" s="2"/>
     </row>
-    <row r="79" ht="14.25" customHeight="1">
+    <row r="79" ht="14.25" customHeight="1" spans="2:32">
       <c r="B79" s="2"/>
       <c r="T79" s="2"/>
       <c r="U79" s="3"/>
@@ -1930,7 +2861,7 @@
       <c r="AE79" s="2"/>
       <c r="AF79" s="2"/>
     </row>
-    <row r="80" ht="14.25" customHeight="1">
+    <row r="80" ht="14.25" customHeight="1" spans="2:32">
       <c r="B80" s="2"/>
       <c r="T80" s="2"/>
       <c r="U80" s="3"/>
@@ -1941,7 +2872,7 @@
       <c r="AE80" s="2"/>
       <c r="AF80" s="2"/>
     </row>
-    <row r="81" ht="14.25" customHeight="1">
+    <row r="81" ht="14.25" customHeight="1" spans="2:32">
       <c r="B81" s="2"/>
       <c r="T81" s="2"/>
       <c r="U81" s="3"/>
@@ -1952,7 +2883,7 @@
       <c r="AE81" s="2"/>
       <c r="AF81" s="2"/>
     </row>
-    <row r="82" ht="14.25" customHeight="1">
+    <row r="82" ht="14.25" customHeight="1" spans="2:32">
       <c r="B82" s="2"/>
       <c r="T82" s="2"/>
       <c r="U82" s="3"/>
@@ -1963,7 +2894,7 @@
       <c r="AE82" s="2"/>
       <c r="AF82" s="2"/>
     </row>
-    <row r="83" ht="14.25" customHeight="1">
+    <row r="83" ht="14.25" customHeight="1" spans="2:32">
       <c r="B83" s="2"/>
       <c r="T83" s="2"/>
       <c r="U83" s="3"/>
@@ -1974,7 +2905,7 @@
       <c r="AE83" s="2"/>
       <c r="AF83" s="2"/>
     </row>
-    <row r="84" ht="14.25" customHeight="1">
+    <row r="84" ht="14.25" customHeight="1" spans="2:32">
       <c r="B84" s="2"/>
       <c r="T84" s="2"/>
       <c r="U84" s="3"/>
@@ -1985,7 +2916,7 @@
       <c r="AE84" s="2"/>
       <c r="AF84" s="2"/>
     </row>
-    <row r="85" ht="14.25" customHeight="1">
+    <row r="85" ht="14.25" customHeight="1" spans="2:32">
       <c r="B85" s="2"/>
       <c r="T85" s="2"/>
       <c r="U85" s="3"/>
@@ -1996,7 +2927,7 @@
       <c r="AE85" s="2"/>
       <c r="AF85" s="2"/>
     </row>
-    <row r="86" ht="14.25" customHeight="1">
+    <row r="86" ht="14.25" customHeight="1" spans="2:32">
       <c r="B86" s="2"/>
       <c r="T86" s="2"/>
       <c r="U86" s="3"/>
@@ -2007,7 +2938,7 @@
       <c r="AE86" s="2"/>
       <c r="AF86" s="2"/>
     </row>
-    <row r="87" ht="14.25" customHeight="1">
+    <row r="87" ht="14.25" customHeight="1" spans="2:32">
       <c r="B87" s="2"/>
       <c r="T87" s="2"/>
       <c r="U87" s="3"/>
@@ -2018,7 +2949,7 @@
       <c r="AE87" s="2"/>
       <c r="AF87" s="2"/>
     </row>
-    <row r="88" ht="14.25" customHeight="1">
+    <row r="88" ht="14.25" customHeight="1" spans="2:32">
       <c r="B88" s="2"/>
       <c r="T88" s="2"/>
       <c r="U88" s="3"/>
@@ -2029,7 +2960,7 @@
       <c r="AE88" s="2"/>
       <c r="AF88" s="2"/>
     </row>
-    <row r="89" ht="14.25" customHeight="1">
+    <row r="89" ht="14.25" customHeight="1" spans="2:32">
       <c r="B89" s="2"/>
       <c r="T89" s="2"/>
       <c r="U89" s="3"/>
@@ -2040,7 +2971,7 @@
       <c r="AE89" s="2"/>
       <c r="AF89" s="2"/>
     </row>
-    <row r="90" ht="14.25" customHeight="1">
+    <row r="90" ht="14.25" customHeight="1" spans="2:32">
       <c r="B90" s="2"/>
       <c r="T90" s="2"/>
       <c r="U90" s="3"/>
@@ -2051,7 +2982,7 @@
       <c r="AE90" s="2"/>
       <c r="AF90" s="2"/>
     </row>
-    <row r="91" ht="14.25" customHeight="1">
+    <row r="91" ht="14.25" customHeight="1" spans="2:32">
       <c r="B91" s="2"/>
       <c r="T91" s="2"/>
       <c r="U91" s="3"/>
@@ -2062,7 +2993,7 @@
       <c r="AE91" s="2"/>
       <c r="AF91" s="2"/>
     </row>
-    <row r="92" ht="14.25" customHeight="1">
+    <row r="92" ht="14.25" customHeight="1" spans="2:32">
       <c r="B92" s="2"/>
       <c r="T92" s="2"/>
       <c r="U92" s="3"/>
@@ -2073,7 +3004,7 @@
       <c r="AE92" s="2"/>
       <c r="AF92" s="2"/>
     </row>
-    <row r="93" ht="14.25" customHeight="1">
+    <row r="93" ht="14.25" customHeight="1" spans="2:32">
       <c r="B93" s="2"/>
       <c r="T93" s="2"/>
       <c r="U93" s="3"/>
@@ -2084,7 +3015,7 @@
       <c r="AE93" s="2"/>
       <c r="AF93" s="2"/>
     </row>
-    <row r="94" ht="14.25" customHeight="1">
+    <row r="94" ht="14.25" customHeight="1" spans="2:32">
       <c r="B94" s="2"/>
       <c r="T94" s="2"/>
       <c r="U94" s="3"/>
@@ -2095,7 +3026,7 @@
       <c r="AE94" s="2"/>
       <c r="AF94" s="2"/>
     </row>
-    <row r="95" ht="14.25" customHeight="1">
+    <row r="95" ht="14.25" customHeight="1" spans="2:32">
       <c r="B95" s="2"/>
       <c r="T95" s="2"/>
       <c r="U95" s="3"/>
@@ -2106,7 +3037,7 @@
       <c r="AE95" s="2"/>
       <c r="AF95" s="2"/>
     </row>
-    <row r="96" ht="14.25" customHeight="1">
+    <row r="96" ht="14.25" customHeight="1" spans="2:32">
       <c r="B96" s="2"/>
       <c r="T96" s="2"/>
       <c r="U96" s="3"/>
@@ -2117,7 +3048,7 @@
       <c r="AE96" s="2"/>
       <c r="AF96" s="2"/>
     </row>
-    <row r="97" ht="14.25" customHeight="1">
+    <row r="97" ht="14.25" customHeight="1" spans="2:32">
       <c r="B97" s="2"/>
       <c r="T97" s="2"/>
       <c r="U97" s="3"/>
@@ -2128,7 +3059,7 @@
       <c r="AE97" s="2"/>
       <c r="AF97" s="2"/>
     </row>
-    <row r="98" ht="14.25" customHeight="1">
+    <row r="98" ht="14.25" customHeight="1" spans="2:32">
       <c r="B98" s="2"/>
       <c r="T98" s="2"/>
       <c r="U98" s="3"/>
@@ -2139,7 +3070,7 @@
       <c r="AE98" s="2"/>
       <c r="AF98" s="2"/>
     </row>
-    <row r="99" ht="14.25" customHeight="1">
+    <row r="99" ht="14.25" customHeight="1" spans="2:32">
       <c r="B99" s="2"/>
       <c r="T99" s="2"/>
       <c r="U99" s="3"/>
@@ -2150,7 +3081,7 @@
       <c r="AE99" s="2"/>
       <c r="AF99" s="2"/>
     </row>
-    <row r="100" ht="14.25" customHeight="1">
+    <row r="100" ht="14.25" customHeight="1" spans="2:32">
       <c r="B100" s="2"/>
       <c r="T100" s="2"/>
       <c r="U100" s="3"/>
@@ -2161,7 +3092,7 @@
       <c r="AE100" s="2"/>
       <c r="AF100" s="2"/>
     </row>
-    <row r="101" ht="14.25" customHeight="1">
+    <row r="101" ht="14.25" customHeight="1" spans="2:32">
       <c r="B101" s="2"/>
       <c r="T101" s="2"/>
       <c r="U101" s="3"/>
@@ -2172,7 +3103,7 @@
       <c r="AE101" s="2"/>
       <c r="AF101" s="2"/>
     </row>
-    <row r="102" ht="14.25" customHeight="1">
+    <row r="102" ht="14.25" customHeight="1" spans="2:32">
       <c r="B102" s="2"/>
       <c r="T102" s="2"/>
       <c r="U102" s="3"/>
@@ -2183,7 +3114,7 @@
       <c r="AE102" s="2"/>
       <c r="AF102" s="2"/>
     </row>
-    <row r="103" ht="14.25" customHeight="1">
+    <row r="103" ht="14.25" customHeight="1" spans="2:32">
       <c r="B103" s="2"/>
       <c r="T103" s="2"/>
       <c r="U103" s="3"/>
@@ -2194,7 +3125,7 @@
       <c r="AE103" s="2"/>
       <c r="AF103" s="2"/>
     </row>
-    <row r="104" ht="14.25" customHeight="1">
+    <row r="104" ht="14.25" customHeight="1" spans="2:32">
       <c r="B104" s="2"/>
       <c r="T104" s="2"/>
       <c r="U104" s="3"/>
@@ -2205,7 +3136,7 @@
       <c r="AE104" s="2"/>
       <c r="AF104" s="2"/>
     </row>
-    <row r="105" ht="14.25" customHeight="1">
+    <row r="105" ht="14.25" customHeight="1" spans="2:32">
       <c r="B105" s="2"/>
       <c r="T105" s="2"/>
       <c r="U105" s="3"/>
@@ -2216,7 +3147,7 @@
       <c r="AE105" s="2"/>
       <c r="AF105" s="2"/>
     </row>
-    <row r="106" ht="14.25" customHeight="1">
+    <row r="106" ht="14.25" customHeight="1" spans="2:32">
       <c r="B106" s="2"/>
       <c r="T106" s="2"/>
       <c r="U106" s="3"/>
@@ -2227,7 +3158,7 @@
       <c r="AE106" s="2"/>
       <c r="AF106" s="2"/>
     </row>
-    <row r="107" ht="14.25" customHeight="1">
+    <row r="107" ht="14.25" customHeight="1" spans="2:32">
       <c r="B107" s="2"/>
       <c r="T107" s="2"/>
       <c r="U107" s="3"/>
@@ -2238,7 +3169,7 @@
       <c r="AE107" s="2"/>
       <c r="AF107" s="2"/>
     </row>
-    <row r="108" ht="14.25" customHeight="1">
+    <row r="108" ht="14.25" customHeight="1" spans="2:32">
       <c r="B108" s="2"/>
       <c r="T108" s="2"/>
       <c r="U108" s="3"/>
@@ -2249,7 +3180,7 @@
       <c r="AE108" s="2"/>
       <c r="AF108" s="2"/>
     </row>
-    <row r="109" ht="14.25" customHeight="1">
+    <row r="109" ht="14.25" customHeight="1" spans="2:32">
       <c r="B109" s="2"/>
       <c r="T109" s="2"/>
       <c r="U109" s="3"/>
@@ -2260,7 +3191,7 @@
       <c r="AE109" s="2"/>
       <c r="AF109" s="2"/>
     </row>
-    <row r="110" ht="14.25" customHeight="1">
+    <row r="110" ht="14.25" customHeight="1" spans="2:32">
       <c r="B110" s="2"/>
       <c r="T110" s="2"/>
       <c r="U110" s="3"/>
@@ -2271,7 +3202,7 @@
       <c r="AE110" s="2"/>
       <c r="AF110" s="2"/>
     </row>
-    <row r="111" ht="14.25" customHeight="1">
+    <row r="111" ht="14.25" customHeight="1" spans="2:32">
       <c r="B111" s="2"/>
       <c r="T111" s="2"/>
       <c r="U111" s="3"/>
@@ -2282,7 +3213,7 @@
       <c r="AE111" s="2"/>
       <c r="AF111" s="2"/>
     </row>
-    <row r="112" ht="14.25" customHeight="1">
+    <row r="112" ht="14.25" customHeight="1" spans="2:32">
       <c r="B112" s="2"/>
       <c r="T112" s="2"/>
       <c r="U112" s="3"/>
@@ -2293,7 +3224,7 @@
       <c r="AE112" s="2"/>
       <c r="AF112" s="2"/>
     </row>
-    <row r="113" ht="14.25" customHeight="1">
+    <row r="113" ht="14.25" customHeight="1" spans="2:32">
       <c r="B113" s="2"/>
       <c r="T113" s="2"/>
       <c r="U113" s="3"/>
@@ -2304,7 +3235,7 @@
       <c r="AE113" s="2"/>
       <c r="AF113" s="2"/>
     </row>
-    <row r="114" ht="14.25" customHeight="1">
+    <row r="114" ht="14.25" customHeight="1" spans="2:32">
       <c r="B114" s="2"/>
       <c r="T114" s="2"/>
       <c r="U114" s="3"/>
@@ -2315,7 +3246,7 @@
       <c r="AE114" s="2"/>
       <c r="AF114" s="2"/>
     </row>
-    <row r="115" ht="14.25" customHeight="1">
+    <row r="115" ht="14.25" customHeight="1" spans="2:32">
       <c r="B115" s="2"/>
       <c r="T115" s="2"/>
       <c r="U115" s="3"/>
@@ -2326,7 +3257,7 @@
       <c r="AE115" s="2"/>
       <c r="AF115" s="2"/>
     </row>
-    <row r="116" ht="14.25" customHeight="1">
+    <row r="116" ht="14.25" customHeight="1" spans="2:32">
       <c r="B116" s="2"/>
       <c r="T116" s="2"/>
       <c r="U116" s="3"/>
@@ -2337,7 +3268,7 @@
       <c r="AE116" s="2"/>
       <c r="AF116" s="2"/>
     </row>
-    <row r="117" ht="14.25" customHeight="1">
+    <row r="117" ht="14.25" customHeight="1" spans="2:32">
       <c r="B117" s="2"/>
       <c r="T117" s="2"/>
       <c r="U117" s="3"/>
@@ -2348,7 +3279,7 @@
       <c r="AE117" s="2"/>
       <c r="AF117" s="2"/>
     </row>
-    <row r="118" ht="14.25" customHeight="1">
+    <row r="118" ht="14.25" customHeight="1" spans="2:32">
       <c r="B118" s="2"/>
       <c r="T118" s="2"/>
       <c r="U118" s="3"/>
@@ -2359,7 +3290,7 @@
       <c r="AE118" s="2"/>
       <c r="AF118" s="2"/>
     </row>
-    <row r="119" ht="14.25" customHeight="1">
+    <row r="119" ht="14.25" customHeight="1" spans="2:32">
       <c r="B119" s="2"/>
       <c r="T119" s="2"/>
       <c r="U119" s="3"/>
@@ -2370,7 +3301,7 @@
       <c r="AE119" s="2"/>
       <c r="AF119" s="2"/>
     </row>
-    <row r="120" ht="14.25" customHeight="1">
+    <row r="120" ht="14.25" customHeight="1" spans="2:32">
       <c r="B120" s="2"/>
       <c r="T120" s="2"/>
       <c r="U120" s="3"/>
@@ -2381,7 +3312,7 @@
       <c r="AE120" s="2"/>
       <c r="AF120" s="2"/>
     </row>
-    <row r="121" ht="14.25" customHeight="1">
+    <row r="121" ht="14.25" customHeight="1" spans="2:32">
       <c r="B121" s="2"/>
       <c r="T121" s="2"/>
       <c r="U121" s="3"/>
@@ -2392,7 +3323,7 @@
       <c r="AE121" s="2"/>
       <c r="AF121" s="2"/>
     </row>
-    <row r="122" ht="14.25" customHeight="1">
+    <row r="122" ht="14.25" customHeight="1" spans="2:32">
       <c r="B122" s="2"/>
       <c r="T122" s="2"/>
       <c r="U122" s="3"/>
@@ -2403,7 +3334,7 @@
       <c r="AE122" s="2"/>
       <c r="AF122" s="2"/>
     </row>
-    <row r="123" ht="14.25" customHeight="1">
+    <row r="123" ht="14.25" customHeight="1" spans="2:32">
       <c r="B123" s="2"/>
       <c r="T123" s="2"/>
       <c r="U123" s="3"/>
@@ -2414,7 +3345,7 @@
       <c r="AE123" s="2"/>
       <c r="AF123" s="2"/>
     </row>
-    <row r="124" ht="14.25" customHeight="1">
+    <row r="124" ht="14.25" customHeight="1" spans="2:32">
       <c r="B124" s="2"/>
       <c r="T124" s="2"/>
       <c r="U124" s="3"/>
@@ -2425,7 +3356,7 @@
       <c r="AE124" s="2"/>
       <c r="AF124" s="2"/>
     </row>
-    <row r="125" ht="14.25" customHeight="1">
+    <row r="125" ht="14.25" customHeight="1" spans="2:32">
       <c r="B125" s="2"/>
       <c r="T125" s="2"/>
       <c r="U125" s="3"/>
@@ -2436,7 +3367,7 @@
       <c r="AE125" s="2"/>
       <c r="AF125" s="2"/>
     </row>
-    <row r="126" ht="14.25" customHeight="1">
+    <row r="126" ht="14.25" customHeight="1" spans="2:32">
       <c r="B126" s="2"/>
       <c r="T126" s="2"/>
       <c r="U126" s="3"/>
@@ -2447,7 +3378,7 @@
       <c r="AE126" s="2"/>
       <c r="AF126" s="2"/>
     </row>
-    <row r="127" ht="14.25" customHeight="1">
+    <row r="127" ht="14.25" customHeight="1" spans="2:32">
       <c r="B127" s="2"/>
       <c r="T127" s="2"/>
       <c r="U127" s="3"/>
@@ -2458,7 +3389,7 @@
       <c r="AE127" s="2"/>
       <c r="AF127" s="2"/>
     </row>
-    <row r="128" ht="14.25" customHeight="1">
+    <row r="128" ht="14.25" customHeight="1" spans="2:32">
       <c r="B128" s="2"/>
       <c r="T128" s="2"/>
       <c r="U128" s="3"/>
@@ -2469,7 +3400,7 @@
       <c r="AE128" s="2"/>
       <c r="AF128" s="2"/>
     </row>
-    <row r="129" ht="14.25" customHeight="1">
+    <row r="129" ht="14.25" customHeight="1" spans="2:32">
       <c r="B129" s="2"/>
       <c r="T129" s="2"/>
       <c r="U129" s="3"/>
@@ -2480,7 +3411,7 @@
       <c r="AE129" s="2"/>
       <c r="AF129" s="2"/>
     </row>
-    <row r="130" ht="14.25" customHeight="1">
+    <row r="130" ht="14.25" customHeight="1" spans="2:32">
       <c r="B130" s="2"/>
       <c r="T130" s="2"/>
       <c r="U130" s="3"/>
@@ -2491,7 +3422,7 @@
       <c r="AE130" s="2"/>
       <c r="AF130" s="2"/>
     </row>
-    <row r="131" ht="14.25" customHeight="1">
+    <row r="131" ht="14.25" customHeight="1" spans="2:32">
       <c r="B131" s="2"/>
       <c r="T131" s="2"/>
       <c r="U131" s="3"/>
@@ -2502,7 +3433,7 @@
       <c r="AE131" s="2"/>
       <c r="AF131" s="2"/>
     </row>
-    <row r="132" ht="14.25" customHeight="1">
+    <row r="132" ht="14.25" customHeight="1" spans="2:32">
       <c r="B132" s="2"/>
       <c r="T132" s="2"/>
       <c r="U132" s="3"/>
@@ -2513,7 +3444,7 @@
       <c r="AE132" s="2"/>
       <c r="AF132" s="2"/>
     </row>
-    <row r="133" ht="14.25" customHeight="1">
+    <row r="133" ht="14.25" customHeight="1" spans="2:32">
       <c r="B133" s="2"/>
       <c r="T133" s="2"/>
       <c r="U133" s="3"/>
@@ -2524,7 +3455,7 @@
       <c r="AE133" s="2"/>
       <c r="AF133" s="2"/>
     </row>
-    <row r="134" ht="14.25" customHeight="1">
+    <row r="134" ht="14.25" customHeight="1" spans="2:32">
       <c r="B134" s="2"/>
       <c r="T134" s="2"/>
       <c r="U134" s="3"/>
@@ -2535,7 +3466,7 @@
       <c r="AE134" s="2"/>
       <c r="AF134" s="2"/>
     </row>
-    <row r="135" ht="14.25" customHeight="1">
+    <row r="135" ht="14.25" customHeight="1" spans="2:32">
       <c r="B135" s="2"/>
       <c r="T135" s="2"/>
       <c r="U135" s="3"/>
@@ -2546,7 +3477,7 @@
       <c r="AE135" s="2"/>
       <c r="AF135" s="2"/>
     </row>
-    <row r="136" ht="14.25" customHeight="1">
+    <row r="136" ht="14.25" customHeight="1" spans="2:32">
       <c r="B136" s="2"/>
       <c r="T136" s="2"/>
       <c r="U136" s="3"/>
@@ -2557,7 +3488,7 @@
       <c r="AE136" s="2"/>
       <c r="AF136" s="2"/>
     </row>
-    <row r="137" ht="14.25" customHeight="1">
+    <row r="137" ht="14.25" customHeight="1" spans="2:32">
       <c r="B137" s="2"/>
       <c r="T137" s="2"/>
       <c r="U137" s="3"/>
@@ -2568,7 +3499,7 @@
       <c r="AE137" s="2"/>
       <c r="AF137" s="2"/>
     </row>
-    <row r="138" ht="14.25" customHeight="1">
+    <row r="138" ht="14.25" customHeight="1" spans="2:32">
       <c r="B138" s="2"/>
       <c r="T138" s="2"/>
       <c r="U138" s="3"/>
@@ -2579,7 +3510,7 @@
       <c r="AE138" s="2"/>
       <c r="AF138" s="2"/>
     </row>
-    <row r="139" ht="14.25" customHeight="1">
+    <row r="139" ht="14.25" customHeight="1" spans="2:32">
       <c r="B139" s="2"/>
       <c r="T139" s="2"/>
       <c r="U139" s="3"/>
@@ -2590,7 +3521,7 @@
       <c r="AE139" s="2"/>
       <c r="AF139" s="2"/>
     </row>
-    <row r="140" ht="14.25" customHeight="1">
+    <row r="140" ht="14.25" customHeight="1" spans="2:32">
       <c r="B140" s="2"/>
       <c r="T140" s="2"/>
       <c r="U140" s="3"/>
@@ -2601,7 +3532,7 @@
       <c r="AE140" s="2"/>
       <c r="AF140" s="2"/>
     </row>
-    <row r="141" ht="14.25" customHeight="1">
+    <row r="141" ht="14.25" customHeight="1" spans="2:32">
       <c r="B141" s="2"/>
       <c r="T141" s="2"/>
       <c r="U141" s="3"/>
@@ -2612,7 +3543,7 @@
       <c r="AE141" s="2"/>
       <c r="AF141" s="2"/>
     </row>
-    <row r="142" ht="14.25" customHeight="1">
+    <row r="142" ht="14.25" customHeight="1" spans="2:32">
       <c r="B142" s="2"/>
       <c r="T142" s="2"/>
       <c r="U142" s="3"/>
@@ -2623,7 +3554,7 @@
       <c r="AE142" s="2"/>
       <c r="AF142" s="2"/>
     </row>
-    <row r="143" ht="14.25" customHeight="1">
+    <row r="143" ht="14.25" customHeight="1" spans="2:32">
       <c r="B143" s="2"/>
       <c r="T143" s="2"/>
       <c r="U143" s="3"/>
@@ -2634,7 +3565,7 @@
       <c r="AE143" s="2"/>
       <c r="AF143" s="2"/>
     </row>
-    <row r="144" ht="14.25" customHeight="1">
+    <row r="144" ht="14.25" customHeight="1" spans="2:32">
       <c r="B144" s="2"/>
       <c r="T144" s="2"/>
       <c r="U144" s="3"/>
@@ -2645,7 +3576,7 @@
       <c r="AE144" s="2"/>
       <c r="AF144" s="2"/>
     </row>
-    <row r="145" ht="14.25" customHeight="1">
+    <row r="145" ht="14.25" customHeight="1" spans="2:32">
       <c r="B145" s="2"/>
       <c r="T145" s="2"/>
       <c r="U145" s="3"/>
@@ -2656,7 +3587,7 @@
       <c r="AE145" s="2"/>
       <c r="AF145" s="2"/>
     </row>
-    <row r="146" ht="14.25" customHeight="1">
+    <row r="146" ht="14.25" customHeight="1" spans="2:32">
       <c r="B146" s="2"/>
       <c r="T146" s="2"/>
       <c r="U146" s="3"/>
@@ -2667,7 +3598,7 @@
       <c r="AE146" s="2"/>
       <c r="AF146" s="2"/>
     </row>
-    <row r="147" ht="14.25" customHeight="1">
+    <row r="147" ht="14.25" customHeight="1" spans="2:32">
       <c r="B147" s="2"/>
       <c r="T147" s="2"/>
       <c r="U147" s="3"/>
@@ -2678,7 +3609,7 @@
       <c r="AE147" s="2"/>
       <c r="AF147" s="2"/>
     </row>
-    <row r="148" ht="14.25" customHeight="1">
+    <row r="148" ht="14.25" customHeight="1" spans="2:32">
       <c r="B148" s="2"/>
       <c r="T148" s="2"/>
       <c r="U148" s="3"/>
@@ -2689,7 +3620,7 @@
       <c r="AE148" s="2"/>
       <c r="AF148" s="2"/>
     </row>
-    <row r="149" ht="14.25" customHeight="1">
+    <row r="149" ht="14.25" customHeight="1" spans="2:32">
       <c r="B149" s="2"/>
       <c r="T149" s="2"/>
       <c r="U149" s="3"/>
@@ -2700,7 +3631,7 @@
       <c r="AE149" s="2"/>
       <c r="AF149" s="2"/>
     </row>
-    <row r="150" ht="14.25" customHeight="1">
+    <row r="150" ht="14.25" customHeight="1" spans="2:32">
       <c r="B150" s="2"/>
       <c r="T150" s="2"/>
       <c r="U150" s="3"/>
@@ -2711,7 +3642,7 @@
       <c r="AE150" s="2"/>
       <c r="AF150" s="2"/>
     </row>
-    <row r="151" ht="14.25" customHeight="1">
+    <row r="151" ht="14.25" customHeight="1" spans="2:32">
       <c r="B151" s="2"/>
       <c r="T151" s="2"/>
       <c r="U151" s="3"/>
@@ -2722,7 +3653,7 @@
       <c r="AE151" s="2"/>
       <c r="AF151" s="2"/>
     </row>
-    <row r="152" ht="14.25" customHeight="1">
+    <row r="152" ht="14.25" customHeight="1" spans="2:32">
       <c r="B152" s="2"/>
       <c r="T152" s="2"/>
       <c r="U152" s="3"/>
@@ -2733,7 +3664,7 @@
       <c r="AE152" s="2"/>
       <c r="AF152" s="2"/>
     </row>
-    <row r="153" ht="14.25" customHeight="1">
+    <row r="153" ht="14.25" customHeight="1" spans="2:32">
       <c r="B153" s="2"/>
       <c r="T153" s="2"/>
       <c r="U153" s="3"/>
@@ -2744,7 +3675,7 @@
       <c r="AE153" s="2"/>
       <c r="AF153" s="2"/>
     </row>
-    <row r="154" ht="14.25" customHeight="1">
+    <row r="154" ht="14.25" customHeight="1" spans="2:32">
       <c r="B154" s="2"/>
       <c r="T154" s="2"/>
       <c r="U154" s="3"/>
@@ -2755,7 +3686,7 @@
       <c r="AE154" s="2"/>
       <c r="AF154" s="2"/>
     </row>
-    <row r="155" ht="14.25" customHeight="1">
+    <row r="155" ht="14.25" customHeight="1" spans="2:32">
       <c r="B155" s="2"/>
       <c r="T155" s="2"/>
       <c r="U155" s="3"/>
@@ -2766,7 +3697,7 @@
       <c r="AE155" s="2"/>
       <c r="AF155" s="2"/>
     </row>
-    <row r="156" ht="14.25" customHeight="1">
+    <row r="156" ht="14.25" customHeight="1" spans="2:32">
       <c r="B156" s="2"/>
       <c r="T156" s="2"/>
       <c r="U156" s="3"/>
@@ -2777,7 +3708,7 @@
       <c r="AE156" s="2"/>
       <c r="AF156" s="2"/>
     </row>
-    <row r="157" ht="14.25" customHeight="1">
+    <row r="157" ht="14.25" customHeight="1" spans="2:32">
       <c r="B157" s="2"/>
       <c r="T157" s="2"/>
       <c r="U157" s="3"/>
@@ -2788,7 +3719,7 @@
       <c r="AE157" s="2"/>
       <c r="AF157" s="2"/>
     </row>
-    <row r="158" ht="14.25" customHeight="1">
+    <row r="158" ht="14.25" customHeight="1" spans="2:32">
       <c r="B158" s="2"/>
       <c r="T158" s="2"/>
       <c r="U158" s="3"/>
@@ -2799,7 +3730,7 @@
       <c r="AE158" s="2"/>
       <c r="AF158" s="2"/>
     </row>
-    <row r="159" ht="14.25" customHeight="1">
+    <row r="159" ht="14.25" customHeight="1" spans="2:32">
       <c r="B159" s="2"/>
       <c r="T159" s="2"/>
       <c r="U159" s="3"/>
@@ -2810,7 +3741,7 @@
       <c r="AE159" s="2"/>
       <c r="AF159" s="2"/>
     </row>
-    <row r="160" ht="14.25" customHeight="1">
+    <row r="160" ht="14.25" customHeight="1" spans="2:32">
       <c r="B160" s="2"/>
       <c r="T160" s="2"/>
       <c r="U160" s="3"/>
@@ -2821,7 +3752,7 @@
       <c r="AE160" s="2"/>
       <c r="AF160" s="2"/>
     </row>
-    <row r="161" ht="14.25" customHeight="1">
+    <row r="161" ht="14.25" customHeight="1" spans="2:32">
       <c r="B161" s="2"/>
       <c r="T161" s="2"/>
       <c r="U161" s="3"/>
@@ -2832,7 +3763,7 @@
       <c r="AE161" s="2"/>
       <c r="AF161" s="2"/>
     </row>
-    <row r="162" ht="14.25" customHeight="1">
+    <row r="162" ht="14.25" customHeight="1" spans="2:32">
       <c r="B162" s="2"/>
       <c r="T162" s="2"/>
       <c r="U162" s="3"/>
@@ -2843,7 +3774,7 @@
       <c r="AE162" s="2"/>
       <c r="AF162" s="2"/>
     </row>
-    <row r="163" ht="14.25" customHeight="1">
+    <row r="163" ht="14.25" customHeight="1" spans="2:32">
       <c r="B163" s="2"/>
       <c r="T163" s="2"/>
       <c r="U163" s="3"/>
@@ -2854,7 +3785,7 @@
       <c r="AE163" s="2"/>
       <c r="AF163" s="2"/>
     </row>
-    <row r="164" ht="14.25" customHeight="1">
+    <row r="164" ht="14.25" customHeight="1" spans="2:32">
       <c r="B164" s="2"/>
       <c r="T164" s="2"/>
       <c r="U164" s="3"/>
@@ -2865,7 +3796,7 @@
       <c r="AE164" s="2"/>
       <c r="AF164" s="2"/>
     </row>
-    <row r="165" ht="14.25" customHeight="1">
+    <row r="165" ht="14.25" customHeight="1" spans="2:32">
       <c r="B165" s="2"/>
       <c r="T165" s="2"/>
       <c r="U165" s="3"/>
@@ -2876,7 +3807,7 @@
       <c r="AE165" s="2"/>
       <c r="AF165" s="2"/>
     </row>
-    <row r="166" ht="14.25" customHeight="1">
+    <row r="166" ht="14.25" customHeight="1" spans="2:32">
       <c r="B166" s="2"/>
       <c r="T166" s="2"/>
       <c r="U166" s="3"/>
@@ -2887,7 +3818,7 @@
       <c r="AE166" s="2"/>
       <c r="AF166" s="2"/>
     </row>
-    <row r="167" ht="14.25" customHeight="1">
+    <row r="167" ht="14.25" customHeight="1" spans="2:32">
       <c r="B167" s="2"/>
       <c r="T167" s="2"/>
       <c r="U167" s="3"/>
@@ -2898,7 +3829,7 @@
       <c r="AE167" s="2"/>
       <c r="AF167" s="2"/>
     </row>
-    <row r="168" ht="14.25" customHeight="1">
+    <row r="168" ht="14.25" customHeight="1" spans="2:32">
       <c r="B168" s="2"/>
       <c r="T168" s="2"/>
       <c r="U168" s="3"/>
@@ -2909,7 +3840,7 @@
       <c r="AE168" s="2"/>
       <c r="AF168" s="2"/>
     </row>
-    <row r="169" ht="14.25" customHeight="1">
+    <row r="169" ht="14.25" customHeight="1" spans="2:32">
       <c r="B169" s="2"/>
       <c r="T169" s="2"/>
       <c r="U169" s="3"/>
@@ -2920,7 +3851,7 @@
       <c r="AE169" s="2"/>
       <c r="AF169" s="2"/>
     </row>
-    <row r="170" ht="14.25" customHeight="1">
+    <row r="170" ht="14.25" customHeight="1" spans="2:32">
       <c r="B170" s="2"/>
       <c r="T170" s="2"/>
       <c r="U170" s="3"/>
@@ -2931,7 +3862,7 @@
       <c r="AE170" s="2"/>
       <c r="AF170" s="2"/>
     </row>
-    <row r="171" ht="14.25" customHeight="1">
+    <row r="171" ht="14.25" customHeight="1" spans="2:32">
       <c r="B171" s="2"/>
       <c r="T171" s="2"/>
       <c r="U171" s="3"/>
@@ -2942,7 +3873,7 @@
       <c r="AE171" s="2"/>
       <c r="AF171" s="2"/>
     </row>
-    <row r="172" ht="14.25" customHeight="1">
+    <row r="172" ht="14.25" customHeight="1" spans="2:32">
       <c r="B172" s="2"/>
       <c r="T172" s="2"/>
       <c r="U172" s="3"/>
@@ -2953,7 +3884,7 @@
       <c r="AE172" s="2"/>
       <c r="AF172" s="2"/>
     </row>
-    <row r="173" ht="14.25" customHeight="1">
+    <row r="173" ht="14.25" customHeight="1" spans="2:32">
       <c r="B173" s="2"/>
       <c r="T173" s="2"/>
       <c r="U173" s="3"/>
@@ -2964,7 +3895,7 @@
       <c r="AE173" s="2"/>
       <c r="AF173" s="2"/>
     </row>
-    <row r="174" ht="14.25" customHeight="1">
+    <row r="174" ht="14.25" customHeight="1" spans="2:32">
       <c r="B174" s="2"/>
       <c r="T174" s="2"/>
       <c r="U174" s="3"/>
@@ -2975,7 +3906,7 @@
       <c r="AE174" s="2"/>
       <c r="AF174" s="2"/>
     </row>
-    <row r="175" ht="14.25" customHeight="1">
+    <row r="175" ht="14.25" customHeight="1" spans="2:32">
       <c r="B175" s="2"/>
       <c r="T175" s="2"/>
       <c r="U175" s="3"/>
@@ -2986,7 +3917,7 @@
       <c r="AE175" s="2"/>
       <c r="AF175" s="2"/>
     </row>
-    <row r="176" ht="14.25" customHeight="1">
+    <row r="176" ht="14.25" customHeight="1" spans="2:32">
       <c r="B176" s="2"/>
       <c r="T176" s="2"/>
       <c r="U176" s="3"/>
@@ -2997,7 +3928,7 @@
       <c r="AE176" s="2"/>
       <c r="AF176" s="2"/>
     </row>
-    <row r="177" ht="14.25" customHeight="1">
+    <row r="177" ht="14.25" customHeight="1" spans="2:32">
       <c r="B177" s="2"/>
       <c r="T177" s="2"/>
       <c r="U177" s="3"/>
@@ -3008,7 +3939,7 @@
       <c r="AE177" s="2"/>
       <c r="AF177" s="2"/>
     </row>
-    <row r="178" ht="14.25" customHeight="1">
+    <row r="178" ht="14.25" customHeight="1" spans="2:32">
       <c r="B178" s="2"/>
       <c r="T178" s="2"/>
       <c r="U178" s="3"/>
@@ -3019,7 +3950,7 @@
       <c r="AE178" s="2"/>
       <c r="AF178" s="2"/>
     </row>
-    <row r="179" ht="14.25" customHeight="1">
+    <row r="179" ht="14.25" customHeight="1" spans="2:32">
       <c r="B179" s="2"/>
       <c r="T179" s="2"/>
       <c r="U179" s="3"/>
@@ -3030,7 +3961,7 @@
       <c r="AE179" s="2"/>
       <c r="AF179" s="2"/>
     </row>
-    <row r="180" ht="14.25" customHeight="1">
+    <row r="180" ht="14.25" customHeight="1" spans="2:32">
       <c r="B180" s="2"/>
       <c r="T180" s="2"/>
       <c r="U180" s="3"/>
@@ -3041,7 +3972,7 @@
       <c r="AE180" s="2"/>
       <c r="AF180" s="2"/>
     </row>
-    <row r="181" ht="14.25" customHeight="1">
+    <row r="181" ht="14.25" customHeight="1" spans="2:32">
       <c r="B181" s="2"/>
       <c r="T181" s="2"/>
       <c r="U181" s="3"/>
@@ -3052,7 +3983,7 @@
       <c r="AE181" s="2"/>
       <c r="AF181" s="2"/>
     </row>
-    <row r="182" ht="14.25" customHeight="1">
+    <row r="182" ht="14.25" customHeight="1" spans="2:32">
       <c r="B182" s="2"/>
       <c r="T182" s="2"/>
       <c r="U182" s="3"/>
@@ -3063,7 +3994,7 @@
       <c r="AE182" s="2"/>
       <c r="AF182" s="2"/>
     </row>
-    <row r="183" ht="14.25" customHeight="1">
+    <row r="183" ht="14.25" customHeight="1" spans="2:32">
       <c r="B183" s="2"/>
       <c r="T183" s="2"/>
       <c r="U183" s="3"/>
@@ -3074,7 +4005,7 @@
       <c r="AE183" s="2"/>
       <c r="AF183" s="2"/>
     </row>
-    <row r="184" ht="14.25" customHeight="1">
+    <row r="184" ht="14.25" customHeight="1" spans="2:32">
       <c r="B184" s="2"/>
       <c r="T184" s="2"/>
       <c r="U184" s="3"/>
@@ -3085,7 +4016,7 @@
       <c r="AE184" s="2"/>
       <c r="AF184" s="2"/>
     </row>
-    <row r="185" ht="14.25" customHeight="1">
+    <row r="185" ht="14.25" customHeight="1" spans="2:32">
       <c r="B185" s="2"/>
       <c r="T185" s="2"/>
       <c r="U185" s="3"/>
@@ -3096,7 +4027,7 @@
       <c r="AE185" s="2"/>
       <c r="AF185" s="2"/>
     </row>
-    <row r="186" ht="14.25" customHeight="1">
+    <row r="186" ht="14.25" customHeight="1" spans="2:32">
       <c r="B186" s="2"/>
       <c r="T186" s="2"/>
       <c r="U186" s="3"/>
@@ -3107,7 +4038,7 @@
       <c r="AE186" s="2"/>
       <c r="AF186" s="2"/>
     </row>
-    <row r="187" ht="14.25" customHeight="1">
+    <row r="187" ht="14.25" customHeight="1" spans="2:32">
       <c r="B187" s="2"/>
       <c r="T187" s="2"/>
       <c r="U187" s="3"/>
@@ -3118,7 +4049,7 @@
       <c r="AE187" s="2"/>
       <c r="AF187" s="2"/>
     </row>
-    <row r="188" ht="14.25" customHeight="1">
+    <row r="188" ht="14.25" customHeight="1" spans="2:32">
       <c r="B188" s="2"/>
       <c r="T188" s="2"/>
       <c r="U188" s="3"/>
@@ -3129,7 +4060,7 @@
       <c r="AE188" s="2"/>
       <c r="AF188" s="2"/>
     </row>
-    <row r="189" ht="14.25" customHeight="1">
+    <row r="189" ht="14.25" customHeight="1" spans="2:32">
       <c r="B189" s="2"/>
       <c r="T189" s="2"/>
       <c r="U189" s="3"/>
@@ -3140,7 +4071,7 @@
       <c r="AE189" s="2"/>
       <c r="AF189" s="2"/>
     </row>
-    <row r="190" ht="14.25" customHeight="1">
+    <row r="190" ht="14.25" customHeight="1" spans="2:32">
       <c r="B190" s="2"/>
       <c r="T190" s="2"/>
       <c r="U190" s="3"/>
@@ -3151,7 +4082,7 @@
       <c r="AE190" s="2"/>
       <c r="AF190" s="2"/>
     </row>
-    <row r="191" ht="14.25" customHeight="1">
+    <row r="191" ht="14.25" customHeight="1" spans="2:32">
       <c r="B191" s="2"/>
       <c r="T191" s="2"/>
       <c r="U191" s="3"/>
@@ -3162,7 +4093,7 @@
       <c r="AE191" s="2"/>
       <c r="AF191" s="2"/>
     </row>
-    <row r="192" ht="14.25" customHeight="1">
+    <row r="192" ht="14.25" customHeight="1" spans="2:32">
       <c r="B192" s="2"/>
       <c r="T192" s="2"/>
       <c r="U192" s="3"/>
@@ -3173,7 +4104,7 @@
       <c r="AE192" s="2"/>
       <c r="AF192" s="2"/>
     </row>
-    <row r="193" ht="14.25" customHeight="1">
+    <row r="193" ht="14.25" customHeight="1" spans="2:32">
       <c r="B193" s="2"/>
       <c r="T193" s="2"/>
       <c r="U193" s="3"/>
@@ -3184,7 +4115,7 @@
       <c r="AE193" s="2"/>
       <c r="AF193" s="2"/>
     </row>
-    <row r="194" ht="14.25" customHeight="1">
+    <row r="194" ht="14.25" customHeight="1" spans="2:32">
       <c r="B194" s="2"/>
       <c r="T194" s="2"/>
       <c r="U194" s="3"/>
@@ -3195,7 +4126,7 @@
       <c r="AE194" s="2"/>
       <c r="AF194" s="2"/>
     </row>
-    <row r="195" ht="14.25" customHeight="1">
+    <row r="195" ht="14.25" customHeight="1" spans="2:32">
       <c r="B195" s="2"/>
       <c r="T195" s="2"/>
       <c r="U195" s="3"/>
@@ -3206,7 +4137,7 @@
       <c r="AE195" s="2"/>
       <c r="AF195" s="2"/>
     </row>
-    <row r="196" ht="14.25" customHeight="1">
+    <row r="196" ht="14.25" customHeight="1" spans="2:32">
       <c r="B196" s="2"/>
       <c r="T196" s="2"/>
       <c r="U196" s="3"/>
@@ -3217,7 +4148,7 @@
       <c r="AE196" s="2"/>
       <c r="AF196" s="2"/>
     </row>
-    <row r="197" ht="14.25" customHeight="1">
+    <row r="197" ht="14.25" customHeight="1" spans="2:32">
       <c r="B197" s="2"/>
       <c r="T197" s="2"/>
       <c r="U197" s="3"/>
@@ -3228,7 +4159,7 @@
       <c r="AE197" s="2"/>
       <c r="AF197" s="2"/>
     </row>
-    <row r="198" ht="14.25" customHeight="1">
+    <row r="198" ht="14.25" customHeight="1" spans="2:32">
       <c r="B198" s="2"/>
       <c r="T198" s="2"/>
       <c r="U198" s="3"/>
@@ -3239,7 +4170,7 @@
       <c r="AE198" s="2"/>
       <c r="AF198" s="2"/>
     </row>
-    <row r="199" ht="14.25" customHeight="1">
+    <row r="199" ht="14.25" customHeight="1" spans="2:32">
       <c r="B199" s="2"/>
       <c r="T199" s="2"/>
       <c r="U199" s="3"/>
@@ -3250,7 +4181,7 @@
       <c r="AE199" s="2"/>
       <c r="AF199" s="2"/>
     </row>
-    <row r="200" ht="14.25" customHeight="1">
+    <row r="200" ht="14.25" customHeight="1" spans="2:32">
       <c r="B200" s="2"/>
       <c r="T200" s="2"/>
       <c r="U200" s="3"/>
@@ -3261,7 +4192,7 @@
       <c r="AE200" s="2"/>
       <c r="AF200" s="2"/>
     </row>
-    <row r="201" ht="14.25" customHeight="1">
+    <row r="201" ht="14.25" customHeight="1" spans="2:32">
       <c r="B201" s="2"/>
       <c r="T201" s="2"/>
       <c r="U201" s="3"/>
@@ -3272,7 +4203,7 @@
       <c r="AE201" s="2"/>
       <c r="AF201" s="2"/>
     </row>
-    <row r="202" ht="14.25" customHeight="1">
+    <row r="202" ht="14.25" customHeight="1" spans="2:32">
       <c r="B202" s="2"/>
       <c r="T202" s="2"/>
       <c r="U202" s="3"/>
@@ -3283,7 +4214,7 @@
       <c r="AE202" s="2"/>
       <c r="AF202" s="2"/>
     </row>
-    <row r="203" ht="14.25" customHeight="1">
+    <row r="203" ht="14.25" customHeight="1" spans="2:32">
       <c r="B203" s="2"/>
       <c r="T203" s="2"/>
       <c r="U203" s="3"/>
@@ -3294,7 +4225,7 @@
       <c r="AE203" s="2"/>
       <c r="AF203" s="2"/>
     </row>
-    <row r="204" ht="14.25" customHeight="1">
+    <row r="204" ht="14.25" customHeight="1" spans="2:32">
       <c r="B204" s="2"/>
       <c r="T204" s="2"/>
       <c r="U204" s="3"/>
@@ -3305,7 +4236,7 @@
       <c r="AE204" s="2"/>
       <c r="AF204" s="2"/>
     </row>
-    <row r="205" ht="14.25" customHeight="1">
+    <row r="205" ht="14.25" customHeight="1" spans="2:32">
       <c r="B205" s="2"/>
       <c r="T205" s="2"/>
       <c r="U205" s="3"/>
@@ -3316,7 +4247,7 @@
       <c r="AE205" s="2"/>
       <c r="AF205" s="2"/>
     </row>
-    <row r="206" ht="14.25" customHeight="1">
+    <row r="206" ht="14.25" customHeight="1" spans="2:32">
       <c r="B206" s="2"/>
       <c r="T206" s="2"/>
       <c r="U206" s="3"/>
@@ -3327,7 +4258,7 @@
       <c r="AE206" s="2"/>
       <c r="AF206" s="2"/>
     </row>
-    <row r="207" ht="14.25" customHeight="1">
+    <row r="207" ht="14.25" customHeight="1" spans="2:32">
       <c r="B207" s="2"/>
       <c r="T207" s="2"/>
       <c r="U207" s="3"/>
@@ -3338,7 +4269,7 @@
       <c r="AE207" s="2"/>
       <c r="AF207" s="2"/>
     </row>
-    <row r="208" ht="14.25" customHeight="1">
+    <row r="208" ht="14.25" customHeight="1" spans="2:32">
       <c r="B208" s="2"/>
       <c r="T208" s="2"/>
       <c r="U208" s="3"/>
@@ -3349,7 +4280,7 @@
       <c r="AE208" s="2"/>
       <c r="AF208" s="2"/>
     </row>
-    <row r="209" ht="14.25" customHeight="1">
+    <row r="209" ht="14.25" customHeight="1" spans="2:32">
       <c r="B209" s="2"/>
       <c r="T209" s="2"/>
       <c r="U209" s="3"/>
@@ -3360,7 +4291,7 @@
       <c r="AE209" s="2"/>
       <c r="AF209" s="2"/>
     </row>
-    <row r="210" ht="14.25" customHeight="1">
+    <row r="210" ht="14.25" customHeight="1" spans="2:32">
       <c r="B210" s="2"/>
       <c r="T210" s="2"/>
       <c r="U210" s="3"/>
@@ -3371,7 +4302,7 @@
       <c r="AE210" s="2"/>
       <c r="AF210" s="2"/>
     </row>
-    <row r="211" ht="14.25" customHeight="1">
+    <row r="211" ht="14.25" customHeight="1" spans="2:32">
       <c r="B211" s="2"/>
       <c r="T211" s="2"/>
       <c r="U211" s="3"/>
@@ -3382,7 +4313,7 @@
       <c r="AE211" s="2"/>
       <c r="AF211" s="2"/>
     </row>
-    <row r="212" ht="14.25" customHeight="1">
+    <row r="212" ht="14.25" customHeight="1" spans="2:32">
       <c r="B212" s="2"/>
       <c r="T212" s="2"/>
       <c r="U212" s="3"/>
@@ -3393,7 +4324,7 @@
       <c r="AE212" s="2"/>
       <c r="AF212" s="2"/>
     </row>
-    <row r="213" ht="14.25" customHeight="1">
+    <row r="213" ht="14.25" customHeight="1" spans="2:32">
       <c r="B213" s="2"/>
       <c r="T213" s="2"/>
       <c r="U213" s="3"/>
@@ -3404,7 +4335,7 @@
       <c r="AE213" s="2"/>
       <c r="AF213" s="2"/>
     </row>
-    <row r="214" ht="14.25" customHeight="1">
+    <row r="214" ht="14.25" customHeight="1" spans="2:32">
       <c r="B214" s="2"/>
       <c r="T214" s="2"/>
       <c r="U214" s="3"/>
@@ -3415,7 +4346,7 @@
       <c r="AE214" s="2"/>
       <c r="AF214" s="2"/>
     </row>
-    <row r="215" ht="14.25" customHeight="1">
+    <row r="215" ht="14.25" customHeight="1" spans="2:32">
       <c r="B215" s="2"/>
       <c r="T215" s="2"/>
       <c r="U215" s="3"/>
@@ -3426,7 +4357,7 @@
       <c r="AE215" s="2"/>
       <c r="AF215" s="2"/>
     </row>
-    <row r="216" ht="14.25" customHeight="1">
+    <row r="216" ht="14.25" customHeight="1" spans="2:32">
       <c r="B216" s="2"/>
       <c r="T216" s="2"/>
       <c r="U216" s="3"/>
@@ -3437,7 +4368,7 @@
       <c r="AE216" s="2"/>
       <c r="AF216" s="2"/>
     </row>
-    <row r="217" ht="14.25" customHeight="1">
+    <row r="217" ht="14.25" customHeight="1" spans="2:32">
       <c r="B217" s="2"/>
       <c r="T217" s="2"/>
       <c r="U217" s="3"/>
@@ -3448,7 +4379,7 @@
       <c r="AE217" s="2"/>
       <c r="AF217" s="2"/>
     </row>
-    <row r="218" ht="14.25" customHeight="1">
+    <row r="218" ht="14.25" customHeight="1" spans="2:32">
       <c r="B218" s="2"/>
       <c r="T218" s="2"/>
       <c r="U218" s="3"/>
@@ -3459,7 +4390,7 @@
       <c r="AE218" s="2"/>
       <c r="AF218" s="2"/>
     </row>
-    <row r="219" ht="14.25" customHeight="1">
+    <row r="219" ht="14.25" customHeight="1" spans="2:32">
       <c r="B219" s="2"/>
       <c r="T219" s="2"/>
       <c r="U219" s="3"/>
@@ -3470,7 +4401,7 @@
       <c r="AE219" s="2"/>
       <c r="AF219" s="2"/>
     </row>
-    <row r="220" ht="14.25" customHeight="1">
+    <row r="220" ht="14.25" customHeight="1" spans="2:32">
       <c r="B220" s="2"/>
       <c r="T220" s="2"/>
       <c r="U220" s="3"/>
@@ -4262,9 +5193,9 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>